--- a/data/Enrollment_Tracker.xlsx
+++ b/data/Enrollment_Tracker.xlsx
@@ -12060,7 +12060,7 @@
         <v>0</v>
       </c>
       <c r="B210" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C210">
         <v>195934</v>
@@ -12113,7 +12113,7 @@
         <v>1</v>
       </c>
       <c r="B211" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C211">
         <v>736452</v>
@@ -12166,7 +12166,7 @@
         <v>2</v>
       </c>
       <c r="B212" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C212">
         <v>712971</v>
@@ -12219,7 +12219,7 @@
         <v>3</v>
       </c>
       <c r="B213" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C213">
         <v>1524695</v>
@@ -12272,7 +12272,7 @@
         <v>4</v>
       </c>
       <c r="B214" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C214">
         <v>10577595</v>
@@ -12325,7 +12325,7 @@
         <v>5</v>
       </c>
       <c r="B215" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C215">
         <v>1054146</v>
@@ -12378,7 +12378,7 @@
         <v>6</v>
       </c>
       <c r="B216" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C216">
         <v>874182</v>
@@ -12431,7 +12431,7 @@
         <v>7</v>
       </c>
       <c r="B217" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C217">
         <v>222823</v>
@@ -12484,7 +12484,7 @@
         <v>8</v>
       </c>
       <c r="B218" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C218">
         <v>222987</v>
@@ -12537,7 +12537,7 @@
         <v>9</v>
       </c>
       <c r="B219" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C219">
         <v>3400007</v>
@@ -12590,7 +12590,7 @@
         <v>10</v>
       </c>
       <c r="B220" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C220">
         <v>1662466</v>
@@ -12643,7 +12643,7 @@
         <v>11</v>
       </c>
       <c r="B221" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C221">
         <v>366500</v>
@@ -12696,7 +12696,7 @@
         <v>12</v>
       </c>
       <c r="B222" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C222">
         <v>589894</v>
@@ -12749,7 +12749,7 @@
         <v>13</v>
       </c>
       <c r="B223" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C223">
         <v>294322</v>
@@ -12802,7 +12802,7 @@
         <v>14</v>
       </c>
       <c r="B224" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C224">
         <v>2661257</v>
@@ -12855,7 +12855,7 @@
         <v>15</v>
       </c>
       <c r="B225" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C225">
         <v>1277765</v>
@@ -12908,7 +12908,7 @@
         <v>16</v>
       </c>
       <c r="B226" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C226">
         <v>317953</v>
@@ -12961,7 +12961,7 @@
         <v>17</v>
       </c>
       <c r="B227" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C227">
         <v>1164950</v>
@@ -13014,7 +13014,7 @@
         <v>18</v>
       </c>
       <c r="B228" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C228">
         <v>1164490</v>
@@ -13067,7 +13067,7 @@
         <v>19</v>
       </c>
       <c r="B229" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C229">
         <v>1363711</v>
@@ -13120,7 +13120,7 @@
         <v>20</v>
       </c>
       <c r="B230" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C230">
         <v>1187556</v>
@@ -13173,7 +13173,7 @@
         <v>21</v>
       </c>
       <c r="B231" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C231">
         <v>312287</v>
@@ -13226,7 +13226,7 @@
         <v>22</v>
       </c>
       <c r="B232" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C232">
         <v>2000953</v>
@@ -13279,7 +13279,7 @@
         <v>23</v>
       </c>
       <c r="B233" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C233">
         <v>1130415</v>
@@ -13332,7 +13332,7 @@
         <v>24</v>
       </c>
       <c r="B234" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C234">
         <v>1113547</v>
@@ -13385,7 +13385,7 @@
         <v>25</v>
       </c>
       <c r="B235" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C235">
         <v>502060</v>
@@ -13438,7 +13438,7 @@
         <v>26</v>
       </c>
       <c r="B236" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C236">
         <v>181100</v>
@@ -13491,7 +13491,7 @@
         <v>27</v>
       </c>
       <c r="B237" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C237">
         <v>2486253</v>
@@ -13544,7 +13544,7 @@
         <v>28</v>
       </c>
       <c r="B238" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C238">
         <v>98607</v>
@@ -13597,7 +13597,7 @@
         <v>29</v>
       </c>
       <c r="B239" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C239">
         <v>296519</v>
@@ -13650,7 +13650,7 @@
         <v>30</v>
       </c>
       <c r="B240" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C240">
         <v>152000</v>
@@ -13703,7 +13703,7 @@
         <v>31</v>
       </c>
       <c r="B241" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C241">
         <v>1491638</v>
@@ -13756,7 +13756,7 @@
         <v>32</v>
       </c>
       <c r="B242" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C242">
         <v>636907</v>
@@ -13809,7 +13809,7 @@
         <v>33</v>
       </c>
       <c r="B243" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C243">
         <v>675955</v>
@@ -13862,7 +13862,7 @@
         <v>34</v>
       </c>
       <c r="B244" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C244">
         <v>5752512</v>
@@ -13915,7 +13915,7 @@
         <v>35</v>
       </c>
       <c r="B245" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C245">
         <v>2400994</v>
@@ -13968,7 +13968,7 @@
         <v>36</v>
       </c>
       <c r="B246" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C246">
         <v>898649</v>
@@ -14021,7 +14021,7 @@
         <v>37</v>
       </c>
       <c r="B247" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C247">
         <v>1094915</v>
@@ -14074,7 +14074,7 @@
         <v>38</v>
       </c>
       <c r="B248" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C248">
         <v>2701242</v>
@@ -14127,7 +14127,7 @@
         <v>39</v>
       </c>
       <c r="B249" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C249">
         <v>256569</v>
@@ -14180,7 +14180,7 @@
         <v>40</v>
       </c>
       <c r="B250" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C250">
         <v>850016</v>
@@ -14233,7 +14233,7 @@
         <v>41</v>
       </c>
       <c r="B251" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C251">
         <v>124467</v>
@@ -14286,7 +14286,7 @@
         <v>42</v>
       </c>
       <c r="B252" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C252">
         <v>1207988</v>
@@ -14339,7 +14339,7 @@
         <v>43</v>
       </c>
       <c r="B253" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C253">
         <v>3643702</v>
@@ -14392,7 +14392,7 @@
         <v>44</v>
       </c>
       <c r="B254" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C254">
         <v>290143</v>
@@ -14445,7 +14445,7 @@
         <v>45</v>
       </c>
       <c r="B255" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C255">
         <v>1463881</v>
@@ -14498,7 +14498,7 @@
         <v>46</v>
       </c>
       <c r="B256" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C256">
         <v>142134</v>
@@ -14551,7 +14551,7 @@
         <v>47</v>
       </c>
       <c r="B257" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C257">
         <v>1727218</v>
@@ -14604,7 +14604,7 @@
         <v>48</v>
       </c>
       <c r="B258" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C258">
         <v>1017266</v>
@@ -14657,7 +14657,7 @@
         <v>49</v>
       </c>
       <c r="B259" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C259">
         <v>448422</v>
@@ -14710,7 +14710,7 @@
         <v>50</v>
       </c>
       <c r="B260" s="3">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C260">
         <v>54202</v>
@@ -14763,7 +14763,7 @@
         <v>63</v>
       </c>
       <c r="B261" s="8">
-        <v>45748</v>
+        <v>46113</v>
       </c>
       <c r="C261" s="1">
         <f>SUM(C210:C260)</f>

--- a/data/Enrollment_Tracker.xlsx
+++ b/data/Enrollment_Tracker.xlsx
@@ -5,24 +5,26 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\inicchitta\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\inicchitta\Documents\Projects\Enrollment Tracking\project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21CB0896-5139-4E73-88DF-3C76820FC34F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B9CDD5F-B90A-488A-B6B1-BD47BA4196DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{ABF58F20-35C5-4B4F-8D44-F14F003A923B}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{ABF58F20-35C5-4B4F-8D44-F14F003A923B}"/>
   </bookViews>
   <sheets>
     <sheet name="Mcaid" sheetId="1" r:id="rId1"/>
     <sheet name="Mcaid Peak Baseline" sheetId="6" r:id="rId2"/>
-    <sheet name="BHP" sheetId="2" r:id="rId3"/>
-    <sheet name="Marketplace" sheetId="3" r:id="rId4"/>
-    <sheet name="Marketplace (2)" sheetId="5" r:id="rId5"/>
-    <sheet name="Marketplace Feb. Effec. Enroll" sheetId="4" r:id="rId6"/>
+    <sheet name="CHIP" sheetId="7" r:id="rId3"/>
+    <sheet name="CHIP Peak Baseline" sheetId="8" r:id="rId4"/>
+    <sheet name="BHP" sheetId="2" r:id="rId5"/>
+    <sheet name="Marketplace" sheetId="3" r:id="rId6"/>
+    <sheet name="Marketplace (2)" sheetId="5" r:id="rId7"/>
+    <sheet name="Marketplace Feb. Effec. Enroll" sheetId="4" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Marketplace!$A$1:$A$313</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Marketplace (2)'!$A$1:$A$313</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Marketplace!$A$1:$A$313</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Marketplace (2)'!$A$1:$A$313</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2279" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2597" uniqueCount="154">
   <si>
     <t>Alaska</t>
   </si>
@@ -505,6 +507,9 @@
   <si>
     <t>Beneficiaries Whose Coverage Was Renewed based on a Renewal Form</t>
   </si>
+  <si>
+    <t>Total CHIP Enrollment</t>
+  </si>
 </sst>
 </file>
 
@@ -9327,14 +9332,14 @@
         <v>1827</v>
       </c>
       <c r="M158" s="11">
-        <f t="shared" ref="M158:M208" si="15">L158/J158</f>
+        <f t="shared" ref="M158:M207" si="15">L158/J158</f>
         <v>0.27803987216557602</v>
       </c>
       <c r="N158">
         <v>4744</v>
       </c>
       <c r="O158" s="11">
-        <f t="shared" ref="O158:O208" si="16">N158/J158</f>
+        <f t="shared" ref="O158:O207" si="16">N158/J158</f>
         <v>0.72196012783442398</v>
       </c>
       <c r="P158">
@@ -9373,7 +9378,7 @@
         <v>20396</v>
       </c>
       <c r="K159" s="4">
-        <f t="shared" ref="K159:K207" si="17">J159/F159</f>
+        <f t="shared" ref="K159:K206" si="17">J159/F159</f>
         <v>0.216077633697771</v>
       </c>
       <c r="L159">
@@ -12094,7 +12099,7 @@
         <v>1814</v>
       </c>
       <c r="M210" s="11">
-        <f t="shared" ref="M210:M261" si="21">L210/J210</f>
+        <f t="shared" ref="M210:M260" si="21">L210/J210</f>
         <v>0.29983471074380164</v>
       </c>
       <c r="N210">
@@ -12140,7 +12145,7 @@
         <v>42256</v>
       </c>
       <c r="K211" s="4">
-        <f t="shared" ref="K211:K261" si="22">J211/F211</f>
+        <f t="shared" ref="K211:K260" si="22">J211/F211</f>
         <v>0.21000004969709621</v>
       </c>
       <c r="L211">
@@ -12154,7 +12159,7 @@
         <v>25621</v>
       </c>
       <c r="O211" s="11">
-        <f t="shared" ref="O211:O260" si="23">N211/J211</f>
+        <f t="shared" ref="O211:O259" si="23">N211/J211</f>
         <v>0.60632809541840216</v>
       </c>
       <c r="P211">
@@ -14766,35 +14771,35 @@
         <v>46113</v>
       </c>
       <c r="C261" s="1">
-        <f>SUM(C210:C260)</f>
+        <f t="shared" ref="C261:J261" si="24">SUM(C210:C260)</f>
         <v>66725217</v>
       </c>
       <c r="D261" s="1">
-        <f>SUM(D210:D260)</f>
+        <f t="shared" si="24"/>
         <v>38489574</v>
       </c>
       <c r="E261" s="1">
-        <f>SUM(E210:E260)</f>
+        <f t="shared" si="24"/>
         <v>5451600</v>
       </c>
       <c r="F261" s="1">
-        <f>SUM(F210:F260)</f>
+        <f t="shared" si="24"/>
         <v>5828803</v>
       </c>
       <c r="G261" s="1">
-        <f>SUM(G210:G260)</f>
+        <f t="shared" si="24"/>
         <v>3990308</v>
       </c>
       <c r="H261" s="1">
-        <f>SUM(H210:H260)</f>
+        <f t="shared" si="24"/>
         <v>2715704</v>
       </c>
       <c r="I261" s="1">
-        <f>SUM(I210:I260)</f>
+        <f t="shared" si="24"/>
         <v>1274604</v>
       </c>
       <c r="J261" s="1">
-        <f>SUM(J210:J260)</f>
+        <f t="shared" si="24"/>
         <v>1142873</v>
       </c>
       <c r="K261" s="9">
@@ -15428,6 +15433,3496 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BE017E0-0CCA-4F1E-AF7D-1E1C72BF1483}">
+  <dimension ref="A1:C261"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C2">
+        <v>12846</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C3">
+        <v>193204</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C4">
+        <v>83497</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C5">
+        <v>112634</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C6">
+        <v>1228746</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C7">
+        <v>140079</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C8">
+        <v>25323</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C9">
+        <v>16284</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C10">
+        <v>13989</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C11">
+        <v>160955</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C12">
+        <v>185500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C13">
+        <v>24762</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C14">
+        <v>84972</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C15">
+        <v>19667</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C16">
+        <v>318336</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C17">
+        <v>122727</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C18">
+        <v>72590</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C19">
+        <v>132867</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C20">
+        <v>137321</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C21">
+        <v>191201</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C22">
+        <v>196621</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C23">
+        <v>27136</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C24">
+        <v>167087</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C25">
+        <v>4226</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C26">
+        <v>133560</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C27">
+        <v>83623</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C28">
+        <v>19767</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C29">
+        <v>344953</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C30">
+        <v>5387</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C31">
+        <v>36847</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C32">
+        <v>18988</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C33">
+        <v>258231</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C34">
+        <v>43713</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C35">
+        <v>47076</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C36">
+        <v>662420</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C37">
+        <v>242337</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C38">
+        <v>79005</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C39">
+        <v>183955</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C40">
+        <v>280410</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C41">
+        <v>33704</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C42">
+        <v>112832</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C43">
+        <v>14418</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C44">
+        <v>181780</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C45">
+        <v>344976</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C46">
+        <v>34612</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C47">
+        <v>193509</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>46</v>
+      </c>
+      <c r="B48" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C48">
+        <v>5393</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>47</v>
+      </c>
+      <c r="B49" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C49">
+        <v>64618</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>48</v>
+      </c>
+      <c r="B50" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C50">
+        <v>99749</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>49</v>
+      </c>
+      <c r="B51" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C51">
+        <v>39681</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>50</v>
+      </c>
+      <c r="B52" s="3">
+        <v>45992</v>
+      </c>
+      <c r="C52">
+        <v>5847</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B53" s="8">
+        <v>45992</v>
+      </c>
+      <c r="C53" s="1">
+        <f>SUM(C2:C52)</f>
+        <v>7243961</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>0</v>
+      </c>
+      <c r="B54" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C54">
+        <v>12869</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>1</v>
+      </c>
+      <c r="B55" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C55">
+        <v>194604</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>2</v>
+      </c>
+      <c r="B56" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C56">
+        <v>84160</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>3</v>
+      </c>
+      <c r="B57" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C57">
+        <v>112545</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>4</v>
+      </c>
+      <c r="B58" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C58">
+        <v>1237976</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>5</v>
+      </c>
+      <c r="B59" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C59">
+        <v>140483</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>6</v>
+      </c>
+      <c r="B60" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C60">
+        <v>25561</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>7</v>
+      </c>
+      <c r="B61" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C61">
+        <v>16165</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>8</v>
+      </c>
+      <c r="B62" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C62">
+        <v>13946</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>9</v>
+      </c>
+      <c r="B63" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C63">
+        <v>163022</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>10</v>
+      </c>
+      <c r="B64" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C64">
+        <v>183456</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>11</v>
+      </c>
+      <c r="B65" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C65">
+        <v>25342</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>12</v>
+      </c>
+      <c r="B66" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C66">
+        <v>84760</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>13</v>
+      </c>
+      <c r="B67" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C67">
+        <v>19587</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>14</v>
+      </c>
+      <c r="B68" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C68">
+        <v>320864</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C69">
+        <v>122313</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>16</v>
+      </c>
+      <c r="B70" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C70">
+        <v>72803</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>17</v>
+      </c>
+      <c r="B71" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C71">
+        <v>134031</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>18</v>
+      </c>
+      <c r="B72" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C72">
+        <v>137043</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>19</v>
+      </c>
+      <c r="B73" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C73">
+        <v>188257</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>20</v>
+      </c>
+      <c r="B74" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C74">
+        <v>196171</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>21</v>
+      </c>
+      <c r="B75" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C75">
+        <v>21431</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>22</v>
+      </c>
+      <c r="B76" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C76">
+        <v>167306</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>23</v>
+      </c>
+      <c r="B77" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C77">
+        <v>4104</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>24</v>
+      </c>
+      <c r="B78" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C78">
+        <v>134247</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>25</v>
+      </c>
+      <c r="B79" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C79">
+        <v>83703</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>26</v>
+      </c>
+      <c r="B80" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C80">
+        <v>19792</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>27</v>
+      </c>
+      <c r="B81" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C81">
+        <v>344352</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>28</v>
+      </c>
+      <c r="B82" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C82">
+        <v>5414</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>29</v>
+      </c>
+      <c r="B83" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C83">
+        <v>37249</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>30</v>
+      </c>
+      <c r="B84" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C84">
+        <v>18907</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>31</v>
+      </c>
+      <c r="B85" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C85">
+        <v>256572</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>32</v>
+      </c>
+      <c r="B86" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C86">
+        <v>44018</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>33</v>
+      </c>
+      <c r="B87" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C87">
+        <v>47335</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>34</v>
+      </c>
+      <c r="B88" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C88">
+        <v>659617</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>35</v>
+      </c>
+      <c r="B89" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C89">
+        <v>242200</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>36</v>
+      </c>
+      <c r="B90" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C90">
+        <v>74717</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>37</v>
+      </c>
+      <c r="B91" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C91">
+        <v>184066</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>38</v>
+      </c>
+      <c r="B92" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C92">
+        <v>278730</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>39</v>
+      </c>
+      <c r="B93" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C93">
+        <v>34013</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>40</v>
+      </c>
+      <c r="B94" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C94">
+        <v>113356</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>41</v>
+      </c>
+      <c r="B95" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C95">
+        <v>14404</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>42</v>
+      </c>
+      <c r="B96" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C96">
+        <v>181049</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>43</v>
+      </c>
+      <c r="B97" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C97">
+        <v>344813</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>44</v>
+      </c>
+      <c r="B98" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C98">
+        <v>34679</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>45</v>
+      </c>
+      <c r="B99" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C99">
+        <v>192709</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>46</v>
+      </c>
+      <c r="B100" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C100">
+        <v>5468</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>47</v>
+      </c>
+      <c r="B101" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C101">
+        <v>65228</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>48</v>
+      </c>
+      <c r="B102" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C102">
+        <v>99940</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>49</v>
+      </c>
+      <c r="B103" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C103">
+        <v>39648</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>50</v>
+      </c>
+      <c r="B104" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C104">
+        <v>6033</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A105" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B105" s="8">
+        <v>46023</v>
+      </c>
+      <c r="C105" s="1">
+        <f>SUM(C54:C104)</f>
+        <v>7241058</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>0</v>
+      </c>
+      <c r="B106" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C106">
+        <v>12855</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>1</v>
+      </c>
+      <c r="B107" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C107">
+        <v>196218</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>2</v>
+      </c>
+      <c r="B108" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C108">
+        <v>83371</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>3</v>
+      </c>
+      <c r="B109" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C109">
+        <v>111400</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>4</v>
+      </c>
+      <c r="B110" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C110">
+        <v>1240954</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>5</v>
+      </c>
+      <c r="B111" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C111">
+        <v>139344</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>6</v>
+      </c>
+      <c r="B112" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C112">
+        <v>25490</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>7</v>
+      </c>
+      <c r="B113" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C113">
+        <v>16190</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>8</v>
+      </c>
+      <c r="B114" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C114">
+        <v>14007</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>9</v>
+      </c>
+      <c r="B115" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C115">
+        <v>165278</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>10</v>
+      </c>
+      <c r="B116" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C116">
+        <v>182012</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>11</v>
+      </c>
+      <c r="B117" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C117">
+        <v>25575</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
+        <v>12</v>
+      </c>
+      <c r="B118" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C118">
+        <v>84704</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>13</v>
+      </c>
+      <c r="B119" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C119">
+        <v>19595</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>14</v>
+      </c>
+      <c r="B120" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C120">
+        <v>321413</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C121">
+        <v>120298</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>16</v>
+      </c>
+      <c r="B122" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C122">
+        <v>72240</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>17</v>
+      </c>
+      <c r="B123" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C123">
+        <v>128641</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>18</v>
+      </c>
+      <c r="B124" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C124">
+        <v>136395</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>19</v>
+      </c>
+      <c r="B125" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C125">
+        <v>183387</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>20</v>
+      </c>
+      <c r="B126" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C126">
+        <v>195444</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>21</v>
+      </c>
+      <c r="B127" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C127">
+        <v>21134</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>22</v>
+      </c>
+      <c r="B128" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C128">
+        <v>166929</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
+        <v>23</v>
+      </c>
+      <c r="B129" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C129">
+        <v>3982</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
+        <v>24</v>
+      </c>
+      <c r="B130" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C130">
+        <v>134390</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
+        <v>25</v>
+      </c>
+      <c r="B131" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C131">
+        <v>83532</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
+        <v>26</v>
+      </c>
+      <c r="B132" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C132">
+        <v>19805</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
+        <v>27</v>
+      </c>
+      <c r="B133" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C133">
+        <v>345689</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
+        <v>28</v>
+      </c>
+      <c r="B134" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C134">
+        <v>5392</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
+        <v>29</v>
+      </c>
+      <c r="B135" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C135">
+        <v>37273</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
+        <v>30</v>
+      </c>
+      <c r="B136" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C136">
+        <v>18985</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A137" t="s">
+        <v>31</v>
+      </c>
+      <c r="B137" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C137">
+        <v>256439</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
+        <v>32</v>
+      </c>
+      <c r="B138" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C138">
+        <v>43909</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
+        <v>33</v>
+      </c>
+      <c r="B139" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C139">
+        <v>47078</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>34</v>
+      </c>
+      <c r="B140" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C140">
+        <v>657439</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
+        <v>35</v>
+      </c>
+      <c r="B141" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C141">
+        <v>242061</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
+        <v>36</v>
+      </c>
+      <c r="B142" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C142">
+        <v>77906</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
+        <v>37</v>
+      </c>
+      <c r="B143" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C143">
+        <v>182827</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
+        <v>38</v>
+      </c>
+      <c r="B144" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C144">
+        <v>278554</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
+        <v>39</v>
+      </c>
+      <c r="B145" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C145">
+        <v>35160</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
+        <v>40</v>
+      </c>
+      <c r="B146" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C146">
+        <v>113491</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
+        <v>41</v>
+      </c>
+      <c r="B147" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C147">
+        <v>14600</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
+        <v>42</v>
+      </c>
+      <c r="B148" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C148">
+        <v>177810</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>43</v>
+      </c>
+      <c r="B149" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C149">
+        <v>345824</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
+        <v>44</v>
+      </c>
+      <c r="B150" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C150">
+        <v>34682</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
+        <v>45</v>
+      </c>
+      <c r="B151" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C151">
+        <v>190873</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
+        <v>46</v>
+      </c>
+      <c r="B152" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C152">
+        <v>5466</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A153" t="s">
+        <v>47</v>
+      </c>
+      <c r="B153" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C153">
+        <v>65723</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A154" t="s">
+        <v>48</v>
+      </c>
+      <c r="B154" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C154">
+        <v>100048</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A155" t="s">
+        <v>49</v>
+      </c>
+      <c r="B155" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C155">
+        <v>39865</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A156" t="s">
+        <v>50</v>
+      </c>
+      <c r="B156" s="3">
+        <v>46054</v>
+      </c>
+      <c r="C156">
+        <v>5981</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A157" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B157" s="8">
+        <v>46054</v>
+      </c>
+      <c r="C157" s="1">
+        <f>SUM(C106:C156)</f>
+        <v>7227658</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A158" t="s">
+        <v>0</v>
+      </c>
+      <c r="B158" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C158">
+        <v>12843</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A159" t="s">
+        <v>1</v>
+      </c>
+      <c r="B159" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C159">
+        <v>197501</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A160" t="s">
+        <v>2</v>
+      </c>
+      <c r="B160" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C160">
+        <v>83573</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A161" t="s">
+        <v>3</v>
+      </c>
+      <c r="B161" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C161">
+        <v>110570</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A162" t="s">
+        <v>4</v>
+      </c>
+      <c r="B162" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C162">
+        <v>1245606</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A163" t="s">
+        <v>5</v>
+      </c>
+      <c r="B163" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C163">
+        <v>139287</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A164" t="s">
+        <v>6</v>
+      </c>
+      <c r="B164" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C164">
+        <v>25649</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A165" t="s">
+        <v>7</v>
+      </c>
+      <c r="B165" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C165">
+        <v>15890</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A166" t="s">
+        <v>8</v>
+      </c>
+      <c r="B166" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C166">
+        <v>13899</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A167" t="s">
+        <v>9</v>
+      </c>
+      <c r="B167" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C167">
+        <v>168078</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A168" t="s">
+        <v>10</v>
+      </c>
+      <c r="B168" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C168">
+        <v>182283</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A169" t="s">
+        <v>11</v>
+      </c>
+      <c r="B169" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C169">
+        <v>25695</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A170" t="s">
+        <v>12</v>
+      </c>
+      <c r="B170" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C170">
+        <v>84083</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A171" t="s">
+        <v>13</v>
+      </c>
+      <c r="B171" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C171">
+        <v>19785</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A172" t="s">
+        <v>14</v>
+      </c>
+      <c r="B172" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C172">
+        <v>319643</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C173">
+        <v>118614</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A174" t="s">
+        <v>16</v>
+      </c>
+      <c r="B174" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C174">
+        <v>71964</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A175" t="s">
+        <v>17</v>
+      </c>
+      <c r="B175" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C175">
+        <v>125960</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A176" t="s">
+        <v>18</v>
+      </c>
+      <c r="B176" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C176">
+        <v>136772</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A177" t="s">
+        <v>19</v>
+      </c>
+      <c r="B177" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C177">
+        <v>178999</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A178" t="s">
+        <v>20</v>
+      </c>
+      <c r="B178" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C178">
+        <v>195018</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A179" t="s">
+        <v>21</v>
+      </c>
+      <c r="B179" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C179">
+        <v>20928</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A180" t="s">
+        <v>22</v>
+      </c>
+      <c r="B180" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C180">
+        <v>167017</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A181" t="s">
+        <v>23</v>
+      </c>
+      <c r="B181" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C181">
+        <v>4037</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A182" t="s">
+        <v>24</v>
+      </c>
+      <c r="B182" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C182">
+        <v>135843</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A183" t="s">
+        <v>25</v>
+      </c>
+      <c r="B183" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C183">
+        <v>83253</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A184" t="s">
+        <v>26</v>
+      </c>
+      <c r="B184" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C184">
+        <v>20037</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A185" t="s">
+        <v>27</v>
+      </c>
+      <c r="B185" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C185">
+        <v>347117</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A186" t="s">
+        <v>28</v>
+      </c>
+      <c r="B186" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C186">
+        <v>5417</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A187" t="s">
+        <v>29</v>
+      </c>
+      <c r="B187" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C187">
+        <v>37455</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A188" t="s">
+        <v>30</v>
+      </c>
+      <c r="B188" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C188">
+        <v>18943</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A189" t="s">
+        <v>31</v>
+      </c>
+      <c r="B189" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C189">
+        <v>257103</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A190" t="s">
+        <v>32</v>
+      </c>
+      <c r="B190" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C190">
+        <v>44111</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A191" t="s">
+        <v>33</v>
+      </c>
+      <c r="B191" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C191">
+        <v>46879</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A192" t="s">
+        <v>34</v>
+      </c>
+      <c r="B192" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C192">
+        <v>652991</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A193" t="s">
+        <v>35</v>
+      </c>
+      <c r="B193" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C193">
+        <v>237707</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A194" t="s">
+        <v>36</v>
+      </c>
+      <c r="B194" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C194">
+        <v>83566</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A195" t="s">
+        <v>37</v>
+      </c>
+      <c r="B195" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C195">
+        <v>182349</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A196" t="s">
+        <v>38</v>
+      </c>
+      <c r="B196" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C196">
+        <v>280272</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A197" t="s">
+        <v>39</v>
+      </c>
+      <c r="B197" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C197">
+        <v>34526</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A198" t="s">
+        <v>40</v>
+      </c>
+      <c r="B198" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C198">
+        <v>112772</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A199" t="s">
+        <v>41</v>
+      </c>
+      <c r="B199" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C199">
+        <v>14739</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A200" t="s">
+        <v>42</v>
+      </c>
+      <c r="B200" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C200">
+        <v>180842</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A201" t="s">
+        <v>43</v>
+      </c>
+      <c r="B201" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C201">
+        <v>334075</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A202" t="s">
+        <v>44</v>
+      </c>
+      <c r="B202" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C202">
+        <v>34610</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A203" t="s">
+        <v>45</v>
+      </c>
+      <c r="B203" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C203">
+        <v>190582</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A204" t="s">
+        <v>46</v>
+      </c>
+      <c r="B204" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C204">
+        <v>5505</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A205" t="s">
+        <v>47</v>
+      </c>
+      <c r="B205" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C205">
+        <v>66336</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A206" t="s">
+        <v>48</v>
+      </c>
+      <c r="B206" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C206">
+        <v>96751</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A207" t="s">
+        <v>49</v>
+      </c>
+      <c r="B207" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C207">
+        <v>39754</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A208" t="s">
+        <v>50</v>
+      </c>
+      <c r="B208" s="3">
+        <v>46082</v>
+      </c>
+      <c r="C208">
+        <v>6152</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A209" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B209" s="8">
+        <v>46082</v>
+      </c>
+      <c r="C209" s="1">
+        <f>SUM(C158:C208)</f>
+        <v>7213381</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A210" t="s">
+        <v>0</v>
+      </c>
+      <c r="B210" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C210">
+        <v>12740</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A211" t="s">
+        <v>1</v>
+      </c>
+      <c r="B211" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C211">
+        <v>198102</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A212" t="s">
+        <v>2</v>
+      </c>
+      <c r="B212" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C212">
+        <v>78477</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A213" t="s">
+        <v>3</v>
+      </c>
+      <c r="B213" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C213">
+        <v>109923</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A214" t="s">
+        <v>4</v>
+      </c>
+      <c r="B214" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C214">
+        <v>1249682</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A215" t="s">
+        <v>5</v>
+      </c>
+      <c r="B215" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C215">
+        <v>137972</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A216" t="s">
+        <v>6</v>
+      </c>
+      <c r="B216" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C216">
+        <v>25570</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A217" t="s">
+        <v>7</v>
+      </c>
+      <c r="B217" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C217">
+        <v>15713</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A218" t="s">
+        <v>8</v>
+      </c>
+      <c r="B218" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C218">
+        <v>13784</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A219" t="s">
+        <v>9</v>
+      </c>
+      <c r="B219" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C219">
+        <v>171606</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A220" t="s">
+        <v>10</v>
+      </c>
+      <c r="B220" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C220">
+        <v>174668</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A221" t="s">
+        <v>11</v>
+      </c>
+      <c r="B221" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C221">
+        <v>26010</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A222" t="s">
+        <v>12</v>
+      </c>
+      <c r="B222" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C222">
+        <v>83517</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A223" t="s">
+        <v>13</v>
+      </c>
+      <c r="B223" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C223">
+        <v>19597</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A224" t="s">
+        <v>14</v>
+      </c>
+      <c r="B224" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C224">
+        <v>304742</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A225" t="s">
+        <v>15</v>
+      </c>
+      <c r="B225" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C225">
+        <v>117023</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A226" t="s">
+        <v>16</v>
+      </c>
+      <c r="B226" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C226">
+        <v>70832</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A227" t="s">
+        <v>17</v>
+      </c>
+      <c r="B227" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C227">
+        <v>119910</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A228" t="s">
+        <v>18</v>
+      </c>
+      <c r="B228" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C228">
+        <v>131808</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A229" t="s">
+        <v>19</v>
+      </c>
+      <c r="B229" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C229">
+        <v>174695</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A230" t="s">
+        <v>20</v>
+      </c>
+      <c r="B230" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C230">
+        <v>196326</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A231" t="s">
+        <v>21</v>
+      </c>
+      <c r="B231" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C231">
+        <v>19858</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A232" t="s">
+        <v>22</v>
+      </c>
+      <c r="B232" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C232">
+        <v>165309</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A233" t="s">
+        <v>23</v>
+      </c>
+      <c r="B233" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C233">
+        <v>3968</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A234" t="s">
+        <v>24</v>
+      </c>
+      <c r="B234" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C234">
+        <v>132415</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A235" t="s">
+        <v>25</v>
+      </c>
+      <c r="B235" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C235">
+        <v>83125</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A236" t="s">
+        <v>26</v>
+      </c>
+      <c r="B236" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C236">
+        <v>19544</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A237" t="s">
+        <v>27</v>
+      </c>
+      <c r="B237" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C237">
+        <v>349014</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A238" t="s">
+        <v>28</v>
+      </c>
+      <c r="B238" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C238">
+        <v>5410</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A239" t="s">
+        <v>29</v>
+      </c>
+      <c r="B239" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C239">
+        <v>35874</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A240" t="s">
+        <v>30</v>
+      </c>
+      <c r="B240" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C240">
+        <v>18915</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A241" t="s">
+        <v>31</v>
+      </c>
+      <c r="B241" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C241">
+        <v>261154</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A242" t="s">
+        <v>32</v>
+      </c>
+      <c r="B242" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C242">
+        <v>42494</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A243" t="s">
+        <v>33</v>
+      </c>
+      <c r="B243" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C243">
+        <v>46080</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A244" t="s">
+        <v>34</v>
+      </c>
+      <c r="B244" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C244">
+        <v>650335</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A245" t="s">
+        <v>35</v>
+      </c>
+      <c r="B245" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C245">
+        <v>232871</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A246" t="s">
+        <v>36</v>
+      </c>
+      <c r="B246" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C246">
+        <v>81057</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A247" t="s">
+        <v>37</v>
+      </c>
+      <c r="B247" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C247">
+        <v>180746</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A248" t="s">
+        <v>38</v>
+      </c>
+      <c r="B248" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C248">
+        <v>277094</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A249" t="s">
+        <v>39</v>
+      </c>
+      <c r="B249" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C249">
+        <v>33766</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A250" t="s">
+        <v>40</v>
+      </c>
+      <c r="B250" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C250">
+        <v>112428</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A251" t="s">
+        <v>41</v>
+      </c>
+      <c r="B251" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C251">
+        <v>14453</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A252" t="s">
+        <v>42</v>
+      </c>
+      <c r="B252" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C252">
+        <v>181381</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A253" t="s">
+        <v>43</v>
+      </c>
+      <c r="B253" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C253">
+        <v>333003</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A254" t="s">
+        <v>44</v>
+      </c>
+      <c r="B254" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C254">
+        <v>34242</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A255" t="s">
+        <v>45</v>
+      </c>
+      <c r="B255" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C255">
+        <v>189054</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A256" t="s">
+        <v>46</v>
+      </c>
+      <c r="B256" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C256">
+        <v>5527</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A257" t="s">
+        <v>47</v>
+      </c>
+      <c r="B257" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C257">
+        <v>61666</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A258" t="s">
+        <v>48</v>
+      </c>
+      <c r="B258" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C258">
+        <v>97222</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A259" t="s">
+        <v>49</v>
+      </c>
+      <c r="B259" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C259">
+        <v>39040</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A260" t="s">
+        <v>50</v>
+      </c>
+      <c r="B260" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C260">
+        <v>6065</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A261" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B261" s="8">
+        <v>46113</v>
+      </c>
+      <c r="C261" s="1">
+        <f>SUM(C210:C260)</f>
+        <v>7145807</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873D0142-E9C6-4992-9A6E-21A65D208859}">
+  <dimension ref="A1:C53"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C2">
+        <v>12150</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C3">
+        <v>205536</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C4">
+        <v>75026</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C5">
+        <v>147213</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C6">
+        <v>1297814</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C7">
+        <v>119896</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C8">
+        <v>13667</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C9">
+        <v>16242</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C10">
+        <v>6541</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C11">
+        <v>87798</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C12">
+        <v>325706</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C13">
+        <v>24181</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C14">
+        <v>69846</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C15">
+        <v>39369</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C16">
+        <v>346416</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C17">
+        <v>136704</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C18">
+        <v>68364</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C19">
+        <v>143601</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C20">
+        <v>189203</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C21">
+        <v>210420</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C22">
+        <v>166163</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C23">
+        <v>15641</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C24">
+        <v>143833</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C25">
+        <v>3313</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C26">
+        <v>39895</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C27">
+        <v>77568</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C28">
+        <v>28814</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C29">
+        <v>300301</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C30">
+        <v>3881</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C31">
+        <v>42529</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C32">
+        <v>23704</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C33">
+        <v>268685</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C34">
+        <v>54184</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C35">
+        <v>55698</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C36">
+        <v>529246</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C37">
+        <v>254452</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C38">
+        <v>143251</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C39">
+        <v>188991</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C40">
+        <v>250984</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C41">
+        <v>37124</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C42">
+        <v>111786</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C43">
+        <v>19452</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C44">
+        <v>148032</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C45">
+        <v>281452</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C46">
+        <v>38339</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C47">
+        <v>192748</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>46</v>
+      </c>
+      <c r="B48" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C48">
+        <v>4584</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>47</v>
+      </c>
+      <c r="B49" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C49">
+        <v>80027</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>48</v>
+      </c>
+      <c r="B50" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C50">
+        <v>79903</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>49</v>
+      </c>
+      <c r="B51" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C51">
+        <v>37872</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>50</v>
+      </c>
+      <c r="B52" s="3">
+        <v>44986</v>
+      </c>
+      <c r="C52">
+        <v>5303</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B53" s="8">
+        <v>44986</v>
+      </c>
+      <c r="C53" s="1">
+        <f>SUM(C2:C52)</f>
+        <v>7163448</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF918180-16E9-4134-A7AF-5A3A237EE9A0}">
   <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -15809,7 +19304,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F500077B-CC04-42DE-B4CB-18359DAB49B8}">
   <dimension ref="A1:R313"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -22612,7 +26107,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9AC6405-B94F-4AB6-9B77-14A04AE8F552}">
   <dimension ref="A1:R313"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -29556,7 +33051,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDE6A8F5-0D2F-4931-A7B3-5A21B2626B66}">
   <dimension ref="A1:D209"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/data/Enrollment_Tracker.xlsx
+++ b/data/Enrollment_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\inicchitta\Documents\Projects\Enrollment Tracking\project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B9CDD5F-B90A-488A-B6B1-BD47BA4196DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F42CCC4A-64CB-4D65-8DF8-D273176EBD5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{ABF58F20-35C5-4B4F-8D44-F14F003A923B}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2597" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2602" uniqueCount="157">
   <si>
     <t>Alaska</t>
   </si>
@@ -510,6 +510,15 @@
   <si>
     <t>Total CHIP Enrollment</t>
   </si>
+  <si>
+    <t>Medicaid and CHIP Child Enrollment</t>
+  </si>
+  <si>
+    <t>Medicaid Child Enrollment</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
 </sst>
 </file>
 
@@ -15434,15 +15443,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BE017E0-0CCA-4F1E-AF7D-1E1C72BF1483}">
-  <dimension ref="A1:C261"/>
+  <dimension ref="A1:E261"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="32.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>51</v>
       </c>
@@ -15452,8 +15463,14 @@
       <c r="C1" s="1" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -15463,8 +15480,15 @@
       <c r="C2">
         <v>12846</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D2">
+        <f>E2-C2</f>
+        <v>72260</v>
+      </c>
+      <c r="E2">
+        <v>85106</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -15474,8 +15498,15 @@
       <c r="C3">
         <v>193204</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D3">
+        <f t="shared" ref="D3:D66" si="0">E3-C3</f>
+        <v>478657</v>
+      </c>
+      <c r="E3">
+        <v>671861</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -15485,8 +15516,15 @@
       <c r="C4">
         <v>83497</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D4">
+        <f t="shared" si="0"/>
+        <v>330927</v>
+      </c>
+      <c r="E4">
+        <v>414424</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -15496,8 +15534,15 @@
       <c r="C5">
         <v>112634</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>621988</v>
+      </c>
+      <c r="E5">
+        <v>734622</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -15507,8 +15552,15 @@
       <c r="C6">
         <v>1228746</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>3374880</v>
+      </c>
+      <c r="E6">
+        <v>4603626</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -15518,8 +15570,15 @@
       <c r="C7">
         <v>140079</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>384018</v>
+      </c>
+      <c r="E7">
+        <v>524097</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -15529,8 +15588,15 @@
       <c r="C8">
         <v>25323</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>339796</v>
+      </c>
+      <c r="E8">
+        <v>365119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -15540,8 +15606,15 @@
       <c r="C9">
         <v>16284</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>77957</v>
+      </c>
+      <c r="E9">
+        <v>94241</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -15551,8 +15624,15 @@
       <c r="C10">
         <v>13989</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>92718</v>
+      </c>
+      <c r="E10">
+        <v>106707</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -15562,8 +15642,15 @@
       <c r="C11">
         <v>160955</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>2156084</v>
+      </c>
+      <c r="E11">
+        <v>2317039</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -15573,8 +15660,15 @@
       <c r="C12">
         <v>185500</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D12">
+        <f t="shared" si="0"/>
+        <v>1122113</v>
+      </c>
+      <c r="E12">
+        <v>1307613</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -15584,8 +15678,15 @@
       <c r="C13">
         <v>24762</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D13">
+        <f t="shared" si="0"/>
+        <v>128215</v>
+      </c>
+      <c r="E13">
+        <v>152977</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -15595,8 +15696,15 @@
       <c r="C14">
         <v>84972</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D14">
+        <f t="shared" si="0"/>
+        <v>244819</v>
+      </c>
+      <c r="E14">
+        <v>329791</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -15606,8 +15714,15 @@
       <c r="C15">
         <v>19667</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D15">
+        <f t="shared" si="0"/>
+        <v>132072</v>
+      </c>
+      <c r="E15">
+        <v>151739</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -15617,8 +15732,15 @@
       <c r="C16">
         <v>318336</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D16">
+        <f t="shared" si="0"/>
+        <v>1033485</v>
+      </c>
+      <c r="E16">
+        <v>1351821</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -15628,8 +15750,15 @@
       <c r="C17">
         <v>122727</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D17">
+        <f t="shared" si="0"/>
+        <v>580536</v>
+      </c>
+      <c r="E17">
+        <v>703263</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -15639,8 +15768,15 @@
       <c r="C18">
         <v>72590</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D18">
+        <f t="shared" si="0"/>
+        <v>203426</v>
+      </c>
+      <c r="E18">
+        <v>276016</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -15650,8 +15786,15 @@
       <c r="C19">
         <v>132867</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D19">
+        <f t="shared" si="0"/>
+        <v>468797</v>
+      </c>
+      <c r="E19">
+        <v>601664</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -15661,8 +15804,15 @@
       <c r="C20">
         <v>137321</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D20">
+        <f t="shared" si="0"/>
+        <v>542015</v>
+      </c>
+      <c r="E20">
+        <v>679336</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -15672,8 +15822,15 @@
       <c r="C21">
         <v>191201</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D21">
+        <f t="shared" si="0"/>
+        <v>495496</v>
+      </c>
+      <c r="E21">
+        <v>686697</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -15683,8 +15840,15 @@
       <c r="C22">
         <v>196621</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D22">
+        <f t="shared" si="0"/>
+        <v>471601</v>
+      </c>
+      <c r="E22">
+        <v>668222</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -15694,8 +15858,15 @@
       <c r="C23">
         <v>27136</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D23">
+        <f t="shared" si="0"/>
+        <v>112126</v>
+      </c>
+      <c r="E23">
+        <v>139262</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -15705,8 +15876,15 @@
       <c r="C24">
         <v>167087</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D24">
+        <f t="shared" si="0"/>
+        <v>719044</v>
+      </c>
+      <c r="E24">
+        <v>886131</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -15716,8 +15894,15 @@
       <c r="C25">
         <v>4226</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D25">
+        <f t="shared" si="0"/>
+        <v>595889</v>
+      </c>
+      <c r="E25">
+        <v>600115</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -15727,8 +15912,15 @@
       <c r="C26">
         <v>133560</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D26">
+        <f t="shared" si="0"/>
+        <v>438709</v>
+      </c>
+      <c r="E26">
+        <v>572269</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -15738,8 +15930,15 @@
       <c r="C27">
         <v>83623</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D27">
+        <f t="shared" si="0"/>
+        <v>309341</v>
+      </c>
+      <c r="E27">
+        <v>392964</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -15749,8 +15948,15 @@
       <c r="C28">
         <v>19767</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D28">
+        <f t="shared" si="0"/>
+        <v>70010</v>
+      </c>
+      <c r="E28">
+        <v>89777</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -15760,8 +15966,15 @@
       <c r="C29">
         <v>344953</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D29">
+        <f t="shared" si="0"/>
+        <v>1076325</v>
+      </c>
+      <c r="E29">
+        <v>1421278</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -15771,8 +15984,15 @@
       <c r="C30">
         <v>5387</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D30">
+        <f t="shared" si="0"/>
+        <v>45451</v>
+      </c>
+      <c r="E30">
+        <v>50838</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -15782,8 +16002,15 @@
       <c r="C31">
         <v>36847</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D31">
+        <f t="shared" si="0"/>
+        <v>133517</v>
+      </c>
+      <c r="E31">
+        <v>170364</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -15793,8 +16020,15 @@
       <c r="C32">
         <v>18988</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D32">
+        <f t="shared" si="0"/>
+        <v>67121</v>
+      </c>
+      <c r="E32">
+        <v>86109</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>31</v>
       </c>
@@ -15804,8 +16038,15 @@
       <c r="C33">
         <v>258231</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D33">
+        <f t="shared" si="0"/>
+        <v>547676</v>
+      </c>
+      <c r="E33">
+        <v>805907</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -15815,8 +16056,15 @@
       <c r="C34">
         <v>43713</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D34">
+        <f t="shared" si="0"/>
+        <v>264832</v>
+      </c>
+      <c r="E34">
+        <v>308545</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -15826,8 +16074,15 @@
       <c r="C35">
         <v>47076</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D35">
+        <f t="shared" si="0"/>
+        <v>268668</v>
+      </c>
+      <c r="E35">
+        <v>315744</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -15837,8 +16092,15 @@
       <c r="C36">
         <v>662420</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D36">
+        <f t="shared" si="0"/>
+        <v>1796810</v>
+      </c>
+      <c r="E36">
+        <v>2459230</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -15848,8 +16110,15 @@
       <c r="C37">
         <v>242337</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D37">
+        <f t="shared" si="0"/>
+        <v>931820</v>
+      </c>
+      <c r="E37">
+        <v>1174157</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>36</v>
       </c>
@@ -15859,8 +16128,15 @@
       <c r="C38">
         <v>79005</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D38">
+        <f t="shared" si="0"/>
+        <v>428820</v>
+      </c>
+      <c r="E38">
+        <v>507825</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -15870,8 +16146,15 @@
       <c r="C39">
         <v>183955</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D39">
+        <f t="shared" si="0"/>
+        <v>286936</v>
+      </c>
+      <c r="E39">
+        <v>470891</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -15881,8 +16164,15 @@
       <c r="C40">
         <v>280410</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D40">
+        <f t="shared" si="0"/>
+        <v>1126771</v>
+      </c>
+      <c r="E40">
+        <v>1407181</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -15892,8 +16182,15 @@
       <c r="C41">
         <v>33704</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D41">
+        <f t="shared" si="0"/>
+        <v>84749</v>
+      </c>
+      <c r="E41">
+        <v>118453</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -15903,8 +16200,15 @@
       <c r="C42">
         <v>112832</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D42">
+        <f t="shared" si="0"/>
+        <v>492210</v>
+      </c>
+      <c r="E42">
+        <v>605042</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>41</v>
       </c>
@@ -15914,8 +16218,15 @@
       <c r="C43">
         <v>14418</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D43">
+        <f t="shared" si="0"/>
+        <v>61966</v>
+      </c>
+      <c r="E43">
+        <v>76384</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>42</v>
       </c>
@@ -15925,8 +16236,15 @@
       <c r="C44">
         <v>181780</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D44">
+        <f t="shared" si="0"/>
+        <v>648081</v>
+      </c>
+      <c r="E44">
+        <v>829861</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -15936,8 +16254,15 @@
       <c r="C45">
         <v>344976</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D45">
+        <f t="shared" si="0"/>
+        <v>2767793</v>
+      </c>
+      <c r="E45">
+        <v>3112769</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -15947,8 +16272,15 @@
       <c r="C46">
         <v>34612</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D46">
+        <f t="shared" si="0"/>
+        <v>131109</v>
+      </c>
+      <c r="E46">
+        <v>165721</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>45</v>
       </c>
@@ -15958,8 +16290,15 @@
       <c r="C47">
         <v>193509</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D47">
+        <f t="shared" si="0"/>
+        <v>606633</v>
+      </c>
+      <c r="E47">
+        <v>800142</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>46</v>
       </c>
@@ -15969,8 +16308,15 @@
       <c r="C48">
         <v>5393</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D48">
+        <f t="shared" si="0"/>
+        <v>51977</v>
+      </c>
+      <c r="E48">
+        <v>57370</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>47</v>
       </c>
@@ -15980,8 +16326,15 @@
       <c r="C49">
         <v>64618</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D49">
+        <f t="shared" si="0"/>
+        <v>753547</v>
+      </c>
+      <c r="E49">
+        <v>818165</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>48</v>
       </c>
@@ -15991,8 +16344,15 @@
       <c r="C50">
         <v>99749</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D50">
+        <f t="shared" si="0"/>
+        <v>436558</v>
+      </c>
+      <c r="E50">
+        <v>536307</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>49</v>
       </c>
@@ -16002,8 +16362,15 @@
       <c r="C51">
         <v>39681</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D51">
+        <f t="shared" si="0"/>
+        <v>155044</v>
+      </c>
+      <c r="E51">
+        <v>194725</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>50</v>
       </c>
@@ -16013,8 +16380,15 @@
       <c r="C52">
         <v>5847</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D52">
+        <f t="shared" si="0"/>
+        <v>34422</v>
+      </c>
+      <c r="E52">
+        <v>40269</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>63</v>
       </c>
@@ -16025,8 +16399,16 @@
         <f>SUM(C2:C52)</f>
         <v>7243961</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D53" s="1">
+        <f>E53-C53</f>
+        <v>28795815</v>
+      </c>
+      <c r="E53" s="1">
+        <f>SUM(E2:E52)</f>
+        <v>36039776</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>0</v>
       </c>
@@ -16036,8 +16418,15 @@
       <c r="C54">
         <v>12869</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D54">
+        <f t="shared" si="0"/>
+        <v>72099</v>
+      </c>
+      <c r="E54">
+        <v>84968</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>1</v>
       </c>
@@ -16047,8 +16436,15 @@
       <c r="C55">
         <v>194604</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D55">
+        <f t="shared" si="0"/>
+        <v>475673</v>
+      </c>
+      <c r="E55">
+        <v>670277</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>2</v>
       </c>
@@ -16058,8 +16454,15 @@
       <c r="C56">
         <v>84160</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D56">
+        <f t="shared" si="0"/>
+        <v>314788</v>
+      </c>
+      <c r="E56">
+        <v>398948</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>3</v>
       </c>
@@ -16069,8 +16472,15 @@
       <c r="C57">
         <v>112545</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D57">
+        <f t="shared" si="0"/>
+        <v>616066</v>
+      </c>
+      <c r="E57">
+        <v>728611</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>4</v>
       </c>
@@ -16080,8 +16490,15 @@
       <c r="C58">
         <v>1237976</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D58">
+        <f t="shared" si="0"/>
+        <v>3344819</v>
+      </c>
+      <c r="E58">
+        <v>4582795</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>5</v>
       </c>
@@ -16091,8 +16508,15 @@
       <c r="C59">
         <v>140483</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D59">
+        <f t="shared" si="0"/>
+        <v>384184</v>
+      </c>
+      <c r="E59">
+        <v>524667</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>6</v>
       </c>
@@ -16102,8 +16526,15 @@
       <c r="C60">
         <v>25561</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D60">
+        <f t="shared" si="0"/>
+        <v>339462</v>
+      </c>
+      <c r="E60">
+        <v>365023</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>7</v>
       </c>
@@ -16113,8 +16544,15 @@
       <c r="C61">
         <v>16165</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D61">
+        <f t="shared" si="0"/>
+        <v>77092</v>
+      </c>
+      <c r="E61">
+        <v>93257</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>8</v>
       </c>
@@ -16124,8 +16562,15 @@
       <c r="C62">
         <v>13946</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D62">
+        <f t="shared" si="0"/>
+        <v>92155</v>
+      </c>
+      <c r="E62">
+        <v>106101</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>9</v>
       </c>
@@ -16135,8 +16580,15 @@
       <c r="C63">
         <v>163022</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D63">
+        <f t="shared" si="0"/>
+        <v>2149852</v>
+      </c>
+      <c r="E63">
+        <v>2312874</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>10</v>
       </c>
@@ -16146,8 +16598,15 @@
       <c r="C64">
         <v>183456</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D64">
+        <f t="shared" si="0"/>
+        <v>1120215</v>
+      </c>
+      <c r="E64">
+        <v>1303671</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>11</v>
       </c>
@@ -16157,8 +16616,15 @@
       <c r="C65">
         <v>25342</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D65">
+        <f t="shared" si="0"/>
+        <v>128004</v>
+      </c>
+      <c r="E65">
+        <v>153346</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>12</v>
       </c>
@@ -16168,8 +16634,15 @@
       <c r="C66">
         <v>84760</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D66">
+        <f t="shared" si="0"/>
+        <v>244633</v>
+      </c>
+      <c r="E66">
+        <v>329393</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>13</v>
       </c>
@@ -16179,8 +16652,15 @@
       <c r="C67">
         <v>19587</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D67">
+        <f t="shared" ref="D67:D130" si="1">E67-C67</f>
+        <v>131618</v>
+      </c>
+      <c r="E67">
+        <v>151205</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>14</v>
       </c>
@@ -16190,8 +16670,15 @@
       <c r="C68">
         <v>320864</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D68">
+        <f t="shared" si="1"/>
+        <v>1026432</v>
+      </c>
+      <c r="E68">
+        <v>1347296</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>15</v>
       </c>
@@ -16201,8 +16688,15 @@
       <c r="C69">
         <v>122313</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D69">
+        <f t="shared" si="1"/>
+        <v>571991</v>
+      </c>
+      <c r="E69">
+        <v>694304</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>16</v>
       </c>
@@ -16212,8 +16706,15 @@
       <c r="C70">
         <v>72803</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D70">
+        <f t="shared" si="1"/>
+        <v>204313</v>
+      </c>
+      <c r="E70">
+        <v>277116</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>17</v>
       </c>
@@ -16223,8 +16724,15 @@
       <c r="C71">
         <v>134031</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D71">
+        <f t="shared" si="1"/>
+        <v>465575</v>
+      </c>
+      <c r="E71">
+        <v>599606</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -16234,8 +16742,15 @@
       <c r="C72">
         <v>137043</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D72">
+        <f t="shared" si="1"/>
+        <v>540363</v>
+      </c>
+      <c r="E72">
+        <v>677406</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>19</v>
       </c>
@@ -16245,8 +16760,15 @@
       <c r="C73">
         <v>188257</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D73">
+        <f t="shared" si="1"/>
+        <v>494694</v>
+      </c>
+      <c r="E73">
+        <v>682951</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>20</v>
       </c>
@@ -16256,8 +16778,15 @@
       <c r="C74">
         <v>196171</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D74">
+        <f t="shared" si="1"/>
+        <v>469788</v>
+      </c>
+      <c r="E74">
+        <v>665959</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>21</v>
       </c>
@@ -16267,8 +16796,15 @@
       <c r="C75">
         <v>21431</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D75">
+        <f t="shared" si="1"/>
+        <v>117119</v>
+      </c>
+      <c r="E75">
+        <v>138550</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>22</v>
       </c>
@@ -16278,8 +16814,15 @@
       <c r="C76">
         <v>167306</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D76">
+        <f t="shared" si="1"/>
+        <v>717135</v>
+      </c>
+      <c r="E76">
+        <v>884441</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>23</v>
       </c>
@@ -16289,8 +16832,15 @@
       <c r="C77">
         <v>4104</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D77">
+        <f t="shared" si="1"/>
+        <v>592845</v>
+      </c>
+      <c r="E77">
+        <v>596949</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>24</v>
       </c>
@@ -16300,8 +16850,15 @@
       <c r="C78">
         <v>134247</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D78">
+        <f t="shared" si="1"/>
+        <v>435543</v>
+      </c>
+      <c r="E78">
+        <v>569790</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>25</v>
       </c>
@@ -16311,8 +16868,15 @@
       <c r="C79">
         <v>83703</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D79">
+        <f t="shared" si="1"/>
+        <v>309019</v>
+      </c>
+      <c r="E79">
+        <v>392722</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>26</v>
       </c>
@@ -16322,8 +16886,15 @@
       <c r="C80">
         <v>19792</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D80">
+        <f t="shared" si="1"/>
+        <v>69677</v>
+      </c>
+      <c r="E80">
+        <v>89469</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>27</v>
       </c>
@@ -16333,8 +16904,15 @@
       <c r="C81">
         <v>344352</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D81">
+        <f t="shared" si="1"/>
+        <v>1068704</v>
+      </c>
+      <c r="E81">
+        <v>1413056</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>28</v>
       </c>
@@ -16344,8 +16922,15 @@
       <c r="C82">
         <v>5414</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D82">
+        <f t="shared" si="1"/>
+        <v>45311</v>
+      </c>
+      <c r="E82">
+        <v>50725</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>29</v>
       </c>
@@ -16355,8 +16940,15 @@
       <c r="C83">
         <v>37249</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D83">
+        <f t="shared" si="1"/>
+        <v>133593</v>
+      </c>
+      <c r="E83">
+        <v>170842</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>30</v>
       </c>
@@ -16366,8 +16958,15 @@
       <c r="C84">
         <v>18907</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D84">
+        <f t="shared" si="1"/>
+        <v>66696</v>
+      </c>
+      <c r="E84">
+        <v>85603</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>31</v>
       </c>
@@ -16377,8 +16976,15 @@
       <c r="C85">
         <v>256572</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D85">
+        <f t="shared" si="1"/>
+        <v>544559</v>
+      </c>
+      <c r="E85">
+        <v>801131</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>32</v>
       </c>
@@ -16388,8 +16994,15 @@
       <c r="C86">
         <v>44018</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D86">
+        <f t="shared" si="1"/>
+        <v>263930</v>
+      </c>
+      <c r="E86">
+        <v>307948</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>33</v>
       </c>
@@ -16399,8 +17012,15 @@
       <c r="C87">
         <v>47335</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D87">
+        <f t="shared" si="1"/>
+        <v>268603</v>
+      </c>
+      <c r="E87">
+        <v>315938</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>34</v>
       </c>
@@ -16410,8 +17030,15 @@
       <c r="C88">
         <v>659617</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D88">
+        <f t="shared" si="1"/>
+        <v>1789550</v>
+      </c>
+      <c r="E88">
+        <v>2449167</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>35</v>
       </c>
@@ -16421,8 +17048,15 @@
       <c r="C89">
         <v>242200</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D89">
+        <f t="shared" si="1"/>
+        <v>920812</v>
+      </c>
+      <c r="E89">
+        <v>1163012</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>36</v>
       </c>
@@ -16432,8 +17066,15 @@
       <c r="C90">
         <v>74717</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D90">
+        <f t="shared" si="1"/>
+        <v>428400</v>
+      </c>
+      <c r="E90">
+        <v>503117</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>37</v>
       </c>
@@ -16443,8 +17084,15 @@
       <c r="C91">
         <v>184066</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D91">
+        <f t="shared" si="1"/>
+        <v>286619</v>
+      </c>
+      <c r="E91">
+        <v>470685</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>38</v>
       </c>
@@ -16454,8 +17102,15 @@
       <c r="C92">
         <v>278730</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D92">
+        <f t="shared" si="1"/>
+        <v>1123907</v>
+      </c>
+      <c r="E92">
+        <v>1402637</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>39</v>
       </c>
@@ -16465,8 +17120,15 @@
       <c r="C93">
         <v>34013</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D93">
+        <f t="shared" si="1"/>
+        <v>84519</v>
+      </c>
+      <c r="E93">
+        <v>118532</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>40</v>
       </c>
@@ -16476,8 +17138,15 @@
       <c r="C94">
         <v>113356</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D94">
+        <f t="shared" si="1"/>
+        <v>489792</v>
+      </c>
+      <c r="E94">
+        <v>603148</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>41</v>
       </c>
@@ -16487,8 +17156,15 @@
       <c r="C95">
         <v>14404</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D95">
+        <f t="shared" si="1"/>
+        <v>62036</v>
+      </c>
+      <c r="E95">
+        <v>76440</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>42</v>
       </c>
@@ -16498,8 +17174,15 @@
       <c r="C96">
         <v>181049</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D96">
+        <f t="shared" si="1"/>
+        <v>648578</v>
+      </c>
+      <c r="E96">
+        <v>829627</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>43</v>
       </c>
@@ -16509,8 +17192,15 @@
       <c r="C97">
         <v>344813</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D97">
+        <f t="shared" si="1"/>
+        <v>2723103</v>
+      </c>
+      <c r="E97">
+        <v>3067916</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>44</v>
       </c>
@@ -16520,8 +17210,15 @@
       <c r="C98">
         <v>34679</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D98">
+        <f t="shared" si="1"/>
+        <v>129843</v>
+      </c>
+      <c r="E98">
+        <v>164522</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>45</v>
       </c>
@@ -16531,8 +17228,15 @@
       <c r="C99">
         <v>192709</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D99">
+        <f t="shared" si="1"/>
+        <v>605113</v>
+      </c>
+      <c r="E99">
+        <v>797822</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>46</v>
       </c>
@@ -16542,8 +17246,15 @@
       <c r="C100">
         <v>5468</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D100">
+        <f t="shared" si="1"/>
+        <v>51885</v>
+      </c>
+      <c r="E100">
+        <v>57353</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>47</v>
       </c>
@@ -16553,8 +17264,15 @@
       <c r="C101">
         <v>65228</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D101">
+        <f t="shared" si="1"/>
+        <v>752454</v>
+      </c>
+      <c r="E101">
+        <v>817682</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>48</v>
       </c>
@@ -16564,8 +17282,15 @@
       <c r="C102">
         <v>99940</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D102">
+        <f t="shared" si="1"/>
+        <v>436411</v>
+      </c>
+      <c r="E102">
+        <v>536351</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>49</v>
       </c>
@@ -16575,8 +17300,15 @@
       <c r="C103">
         <v>39648</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D103">
+        <f t="shared" si="1"/>
+        <v>154501</v>
+      </c>
+      <c r="E103">
+        <v>194149</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>50</v>
       </c>
@@ -16586,8 +17318,15 @@
       <c r="C104">
         <v>6033</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D104">
+        <f t="shared" si="1"/>
+        <v>34647</v>
+      </c>
+      <c r="E104">
+        <v>40680</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
         <v>63</v>
       </c>
@@ -16598,8 +17337,16 @@
         <f>SUM(C54:C104)</f>
         <v>7241058</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D105" s="1">
+        <f>E105-C105</f>
+        <v>28618720</v>
+      </c>
+      <c r="E105" s="1">
+        <f>SUM(E54:E104)</f>
+        <v>35859778</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>0</v>
       </c>
@@ -16609,8 +17356,15 @@
       <c r="C106">
         <v>12855</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D106">
+        <f t="shared" si="1"/>
+        <v>72317</v>
+      </c>
+      <c r="E106">
+        <v>85172</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>1</v>
       </c>
@@ -16620,8 +17374,15 @@
       <c r="C107">
         <v>196218</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D107">
+        <f t="shared" si="1"/>
+        <v>475064</v>
+      </c>
+      <c r="E107">
+        <v>671282</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>2</v>
       </c>
@@ -16631,8 +17392,15 @@
       <c r="C108">
         <v>83371</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D108">
+        <f t="shared" si="1"/>
+        <v>315988</v>
+      </c>
+      <c r="E108">
+        <v>399359</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>3</v>
       </c>
@@ -16642,8 +17410,15 @@
       <c r="C109">
         <v>111400</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D109">
+        <f t="shared" si="1"/>
+        <v>608244</v>
+      </c>
+      <c r="E109">
+        <v>719644</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>4</v>
       </c>
@@ -16653,8 +17428,15 @@
       <c r="C110">
         <v>1240954</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D110">
+        <f t="shared" si="1"/>
+        <v>3317153</v>
+      </c>
+      <c r="E110">
+        <v>4558107</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>5</v>
       </c>
@@ -16664,8 +17446,15 @@
       <c r="C111">
         <v>139344</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D111">
+        <f t="shared" si="1"/>
+        <v>385082</v>
+      </c>
+      <c r="E111">
+        <v>524426</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>6</v>
       </c>
@@ -16675,8 +17464,15 @@
       <c r="C112">
         <v>25490</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D112">
+        <f t="shared" si="1"/>
+        <v>338537</v>
+      </c>
+      <c r="E112">
+        <v>364027</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>7</v>
       </c>
@@ -16686,8 +17482,15 @@
       <c r="C113">
         <v>16190</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D113">
+        <f t="shared" si="1"/>
+        <v>77518</v>
+      </c>
+      <c r="E113">
+        <v>93708</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>8</v>
       </c>
@@ -16697,8 +17500,15 @@
       <c r="C114">
         <v>14007</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D114">
+        <f t="shared" si="1"/>
+        <v>91635</v>
+      </c>
+      <c r="E114">
+        <v>105642</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>9</v>
       </c>
@@ -16708,8 +17518,15 @@
       <c r="C115">
         <v>165278</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D115">
+        <f t="shared" si="1"/>
+        <v>2138601</v>
+      </c>
+      <c r="E115">
+        <v>2303879</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>10</v>
       </c>
@@ -16719,8 +17536,15 @@
       <c r="C116">
         <v>182012</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D116">
+        <f t="shared" si="1"/>
+        <v>1113757</v>
+      </c>
+      <c r="E116">
+        <v>1295769</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>11</v>
       </c>
@@ -16730,8 +17554,15 @@
       <c r="C117">
         <v>25575</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D117">
+        <f t="shared" si="1"/>
+        <v>127997</v>
+      </c>
+      <c r="E117">
+        <v>153572</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>12</v>
       </c>
@@ -16741,8 +17572,15 @@
       <c r="C118">
         <v>84704</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D118">
+        <f t="shared" si="1"/>
+        <v>246679</v>
+      </c>
+      <c r="E118">
+        <v>331383</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>13</v>
       </c>
@@ -16752,8 +17590,15 @@
       <c r="C119">
         <v>19595</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D119">
+        <f t="shared" si="1"/>
+        <v>131484</v>
+      </c>
+      <c r="E119">
+        <v>151079</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>14</v>
       </c>
@@ -16763,8 +17608,15 @@
       <c r="C120">
         <v>321413</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D120">
+        <f t="shared" si="1"/>
+        <v>1023998</v>
+      </c>
+      <c r="E120">
+        <v>1345411</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>15</v>
       </c>
@@ -16774,8 +17626,15 @@
       <c r="C121">
         <v>120298</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D121">
+        <f t="shared" si="1"/>
+        <v>563260</v>
+      </c>
+      <c r="E121">
+        <v>683558</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>16</v>
       </c>
@@ -16785,8 +17644,15 @@
       <c r="C122">
         <v>72240</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D122">
+        <f t="shared" si="1"/>
+        <v>203324</v>
+      </c>
+      <c r="E122">
+        <v>275564</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>17</v>
       </c>
@@ -16796,8 +17662,15 @@
       <c r="C123">
         <v>128641</v>
       </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D123">
+        <f t="shared" si="1"/>
+        <v>457847</v>
+      </c>
+      <c r="E123">
+        <v>586488</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>18</v>
       </c>
@@ -16807,8 +17680,15 @@
       <c r="C124">
         <v>136395</v>
       </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D124">
+        <f t="shared" si="1"/>
+        <v>534194</v>
+      </c>
+      <c r="E124">
+        <v>670589</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>19</v>
       </c>
@@ -16818,8 +17698,15 @@
       <c r="C125">
         <v>183387</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D125">
+        <f t="shared" si="1"/>
+        <v>492255</v>
+      </c>
+      <c r="E125">
+        <v>675642</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>20</v>
       </c>
@@ -16829,8 +17716,15 @@
       <c r="C126">
         <v>195444</v>
       </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D126">
+        <f t="shared" si="1"/>
+        <v>468756</v>
+      </c>
+      <c r="E126">
+        <v>664200</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>21</v>
       </c>
@@ -16840,8 +17734,15 @@
       <c r="C127">
         <v>21134</v>
       </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D127">
+        <f t="shared" si="1"/>
+        <v>117231</v>
+      </c>
+      <c r="E127">
+        <v>138365</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>22</v>
       </c>
@@ -16851,8 +17752,15 @@
       <c r="C128">
         <v>166929</v>
       </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D128">
+        <f t="shared" si="1"/>
+        <v>714946</v>
+      </c>
+      <c r="E128">
+        <v>881875</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>23</v>
       </c>
@@ -16862,8 +17770,15 @@
       <c r="C129">
         <v>3982</v>
       </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D129">
+        <f t="shared" si="1"/>
+        <v>591420</v>
+      </c>
+      <c r="E129">
+        <v>595402</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>24</v>
       </c>
@@ -16873,8 +17788,15 @@
       <c r="C130">
         <v>134390</v>
       </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D130">
+        <f t="shared" si="1"/>
+        <v>430273</v>
+      </c>
+      <c r="E130">
+        <v>564663</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>25</v>
       </c>
@@ -16884,8 +17806,15 @@
       <c r="C131">
         <v>83532</v>
       </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D131">
+        <f t="shared" ref="D131:D194" si="2">E131-C131</f>
+        <v>308430</v>
+      </c>
+      <c r="E131">
+        <v>391962</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>26</v>
       </c>
@@ -16895,8 +17824,15 @@
       <c r="C132">
         <v>19805</v>
       </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D132">
+        <f t="shared" si="2"/>
+        <v>69450</v>
+      </c>
+      <c r="E132">
+        <v>89255</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>27</v>
       </c>
@@ -16906,8 +17842,15 @@
       <c r="C133">
         <v>345689</v>
       </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D133">
+        <f t="shared" si="2"/>
+        <v>1056396</v>
+      </c>
+      <c r="E133">
+        <v>1402085</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>28</v>
       </c>
@@ -16917,8 +17860,15 @@
       <c r="C134">
         <v>5392</v>
       </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D134">
+        <f t="shared" si="2"/>
+        <v>45306</v>
+      </c>
+      <c r="E134">
+        <v>50698</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>29</v>
       </c>
@@ -16928,8 +17878,15 @@
       <c r="C135">
         <v>37273</v>
       </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D135">
+        <f t="shared" si="2"/>
+        <v>134038</v>
+      </c>
+      <c r="E135">
+        <v>171311</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>30</v>
       </c>
@@ -16939,8 +17896,15 @@
       <c r="C136">
         <v>18985</v>
       </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D136">
+        <f t="shared" si="2"/>
+        <v>66196</v>
+      </c>
+      <c r="E136">
+        <v>85181</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>31</v>
       </c>
@@ -16950,8 +17914,15 @@
       <c r="C137">
         <v>256439</v>
       </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D137">
+        <f t="shared" si="2"/>
+        <v>544891</v>
+      </c>
+      <c r="E137">
+        <v>801330</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>32</v>
       </c>
@@ -16961,8 +17932,15 @@
       <c r="C138">
         <v>43909</v>
       </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D138">
+        <f t="shared" si="2"/>
+        <v>263410</v>
+      </c>
+      <c r="E138">
+        <v>307319</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>33</v>
       </c>
@@ -16972,8 +17950,15 @@
       <c r="C139">
         <v>47078</v>
       </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D139">
+        <f t="shared" si="2"/>
+        <v>267732</v>
+      </c>
+      <c r="E139">
+        <v>314810</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>34</v>
       </c>
@@ -16983,8 +17968,15 @@
       <c r="C140">
         <v>657439</v>
       </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D140">
+        <f t="shared" si="2"/>
+        <v>1776166</v>
+      </c>
+      <c r="E140">
+        <v>2433605</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>35</v>
       </c>
@@ -16994,8 +17986,15 @@
       <c r="C141">
         <v>242061</v>
       </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D141">
+        <f t="shared" si="2"/>
+        <v>911320</v>
+      </c>
+      <c r="E141">
+        <v>1153381</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>36</v>
       </c>
@@ -17005,8 +18004,15 @@
       <c r="C142">
         <v>77906</v>
       </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D142">
+        <f t="shared" si="2"/>
+        <v>423051</v>
+      </c>
+      <c r="E142">
+        <v>500957</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>37</v>
       </c>
@@ -17016,8 +18022,15 @@
       <c r="C143">
         <v>182827</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D143">
+        <f t="shared" si="2"/>
+        <v>286705</v>
+      </c>
+      <c r="E143">
+        <v>469532</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>38</v>
       </c>
@@ -17027,8 +18040,15 @@
       <c r="C144">
         <v>278554</v>
       </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D144">
+        <f t="shared" si="2"/>
+        <v>1127110</v>
+      </c>
+      <c r="E144">
+        <v>1405664</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>39</v>
       </c>
@@ -17038,8 +18058,15 @@
       <c r="C145">
         <v>35160</v>
       </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D145">
+        <f t="shared" si="2"/>
+        <v>78105</v>
+      </c>
+      <c r="E145">
+        <v>113265</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>40</v>
       </c>
@@ -17049,8 +18076,15 @@
       <c r="C146">
         <v>113491</v>
       </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D146">
+        <f t="shared" si="2"/>
+        <v>486261</v>
+      </c>
+      <c r="E146">
+        <v>599752</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>41</v>
       </c>
@@ -17060,8 +18094,15 @@
       <c r="C147">
         <v>14600</v>
       </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D147">
+        <f t="shared" si="2"/>
+        <v>61979</v>
+      </c>
+      <c r="E147">
+        <v>76579</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>42</v>
       </c>
@@ -17071,8 +18112,15 @@
       <c r="C148">
         <v>177810</v>
       </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D148">
+        <f t="shared" si="2"/>
+        <v>650822</v>
+      </c>
+      <c r="E148">
+        <v>828632</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>43</v>
       </c>
@@ -17082,8 +18130,15 @@
       <c r="C149">
         <v>345824</v>
       </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D149">
+        <f t="shared" si="2"/>
+        <v>2693121</v>
+      </c>
+      <c r="E149">
+        <v>3038945</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>44</v>
       </c>
@@ -17093,8 +18148,15 @@
       <c r="C150">
         <v>34682</v>
       </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D150">
+        <f t="shared" si="2"/>
+        <v>129137</v>
+      </c>
+      <c r="E150">
+        <v>163819</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>45</v>
       </c>
@@ -17104,8 +18166,15 @@
       <c r="C151">
         <v>190873</v>
       </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D151">
+        <f t="shared" si="2"/>
+        <v>602188</v>
+      </c>
+      <c r="E151">
+        <v>793061</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>46</v>
       </c>
@@ -17115,8 +18184,15 @@
       <c r="C152">
         <v>5466</v>
       </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D152">
+        <f t="shared" si="2"/>
+        <v>51783</v>
+      </c>
+      <c r="E152">
+        <v>57249</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>47</v>
       </c>
@@ -17126,8 +18202,15 @@
       <c r="C153">
         <v>65723</v>
       </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D153">
+        <f t="shared" si="2"/>
+        <v>750591</v>
+      </c>
+      <c r="E153">
+        <v>816314</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>48</v>
       </c>
@@ -17137,8 +18220,15 @@
       <c r="C154">
         <v>100048</v>
       </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D154">
+        <f t="shared" si="2"/>
+        <v>436255</v>
+      </c>
+      <c r="E154">
+        <v>536303</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>49</v>
       </c>
@@ -17148,8 +18238,15 @@
       <c r="C155">
         <v>39865</v>
       </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D155">
+        <f t="shared" si="2"/>
+        <v>154098</v>
+      </c>
+      <c r="E155">
+        <v>193963</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>50</v>
       </c>
@@ -17159,8 +18256,15 @@
       <c r="C156">
         <v>5981</v>
       </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D156">
+        <f t="shared" si="2"/>
+        <v>34019</v>
+      </c>
+      <c r="E156">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A157" s="1" t="s">
         <v>63</v>
       </c>
@@ -17171,8 +18275,16 @@
         <f>SUM(C106:C156)</f>
         <v>7227658</v>
       </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D157" s="1">
+        <f t="shared" si="2"/>
+        <v>28446120</v>
+      </c>
+      <c r="E157" s="1">
+        <f>SUM(E106:E156)</f>
+        <v>35673778</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>0</v>
       </c>
@@ -17182,8 +18294,15 @@
       <c r="C158">
         <v>12843</v>
       </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D158">
+        <f t="shared" si="2"/>
+        <v>71801</v>
+      </c>
+      <c r="E158">
+        <v>84644</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>1</v>
       </c>
@@ -17193,8 +18312,15 @@
       <c r="C159">
         <v>197501</v>
       </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D159">
+        <f t="shared" si="2"/>
+        <v>473835</v>
+      </c>
+      <c r="E159">
+        <v>671336</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>2</v>
       </c>
@@ -17204,8 +18330,15 @@
       <c r="C160">
         <v>83573</v>
       </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D160">
+        <f t="shared" si="2"/>
+        <v>315638</v>
+      </c>
+      <c r="E160">
+        <v>399211</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>3</v>
       </c>
@@ -17215,8 +18348,15 @@
       <c r="C161">
         <v>110570</v>
       </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D161">
+        <f t="shared" si="2"/>
+        <v>607087</v>
+      </c>
+      <c r="E161">
+        <v>717657</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>4</v>
       </c>
@@ -17226,8 +18366,15 @@
       <c r="C162">
         <v>1245606</v>
       </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D162">
+        <f t="shared" si="2"/>
+        <v>3276885</v>
+      </c>
+      <c r="E162">
+        <v>4522491</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>5</v>
       </c>
@@ -17237,8 +18384,15 @@
       <c r="C163">
         <v>139287</v>
       </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D163">
+        <f t="shared" si="2"/>
+        <v>385198</v>
+      </c>
+      <c r="E163">
+        <v>524485</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>6</v>
       </c>
@@ -17248,8 +18402,15 @@
       <c r="C164">
         <v>25649</v>
       </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D164">
+        <f t="shared" si="2"/>
+        <v>338003</v>
+      </c>
+      <c r="E164">
+        <v>363652</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>7</v>
       </c>
@@ -17259,8 +18420,15 @@
       <c r="C165">
         <v>15890</v>
       </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D165">
+        <f t="shared" si="2"/>
+        <v>77324</v>
+      </c>
+      <c r="E165">
+        <v>93214</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>8</v>
       </c>
@@ -17270,8 +18438,15 @@
       <c r="C166">
         <v>13899</v>
       </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D166">
+        <f t="shared" si="2"/>
+        <v>91459</v>
+      </c>
+      <c r="E166">
+        <v>105358</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>9</v>
       </c>
@@ -17281,8 +18456,15 @@
       <c r="C167">
         <v>168078</v>
       </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D167">
+        <f t="shared" si="2"/>
+        <v>2126301</v>
+      </c>
+      <c r="E167">
+        <v>2294379</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>10</v>
       </c>
@@ -17292,8 +18474,15 @@
       <c r="C168">
         <v>182283</v>
       </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D168">
+        <f t="shared" si="2"/>
+        <v>1111894</v>
+      </c>
+      <c r="E168">
+        <v>1294177</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>11</v>
       </c>
@@ -17303,8 +18492,15 @@
       <c r="C169">
         <v>25695</v>
       </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D169">
+        <f t="shared" si="2"/>
+        <v>128062</v>
+      </c>
+      <c r="E169">
+        <v>153757</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>12</v>
       </c>
@@ -17314,8 +18510,15 @@
       <c r="C170">
         <v>84083</v>
       </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D170">
+        <f t="shared" si="2"/>
+        <v>248265</v>
+      </c>
+      <c r="E170">
+        <v>332348</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>13</v>
       </c>
@@ -17325,8 +18528,15 @@
       <c r="C171">
         <v>19785</v>
       </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D171">
+        <f t="shared" si="2"/>
+        <v>132957</v>
+      </c>
+      <c r="E171">
+        <v>152742</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>14</v>
       </c>
@@ -17336,8 +18546,15 @@
       <c r="C172">
         <v>319643</v>
       </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D172">
+        <f t="shared" si="2"/>
+        <v>1020895</v>
+      </c>
+      <c r="E172">
+        <v>1340538</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>15</v>
       </c>
@@ -17347,8 +18564,15 @@
       <c r="C173">
         <v>118614</v>
       </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D173">
+        <f t="shared" si="2"/>
+        <v>553540</v>
+      </c>
+      <c r="E173">
+        <v>672154</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>16</v>
       </c>
@@ -17358,8 +18582,15 @@
       <c r="C174">
         <v>71964</v>
       </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D174">
+        <f t="shared" si="2"/>
+        <v>203788</v>
+      </c>
+      <c r="E174">
+        <v>275752</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>17</v>
       </c>
@@ -17369,8 +18600,15 @@
       <c r="C175">
         <v>125960</v>
       </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D175">
+        <f t="shared" si="2"/>
+        <v>450131</v>
+      </c>
+      <c r="E175">
+        <v>576091</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>18</v>
       </c>
@@ -17380,8 +18618,15 @@
       <c r="C176">
         <v>136772</v>
       </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D176">
+        <f t="shared" si="2"/>
+        <v>532637</v>
+      </c>
+      <c r="E176">
+        <v>669409</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>19</v>
       </c>
@@ -17391,8 +18636,15 @@
       <c r="C177">
         <v>178999</v>
       </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D177">
+        <f t="shared" si="2"/>
+        <v>490210</v>
+      </c>
+      <c r="E177">
+        <v>669209</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>20</v>
       </c>
@@ -17402,8 +18654,15 @@
       <c r="C178">
         <v>195018</v>
       </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D178">
+        <f t="shared" si="2"/>
+        <v>469939</v>
+      </c>
+      <c r="E178">
+        <v>664957</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>21</v>
       </c>
@@ -17413,8 +18672,15 @@
       <c r="C179">
         <v>20928</v>
       </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D179">
+        <f t="shared" si="2"/>
+        <v>117349</v>
+      </c>
+      <c r="E179">
+        <v>138277</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>22</v>
       </c>
@@ -17424,8 +18690,15 @@
       <c r="C180">
         <v>167017</v>
       </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D180">
+        <f t="shared" si="2"/>
+        <v>715034</v>
+      </c>
+      <c r="E180">
+        <v>882051</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>23</v>
       </c>
@@ -17435,8 +18708,15 @@
       <c r="C181">
         <v>4037</v>
       </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D181">
+        <f t="shared" si="2"/>
+        <v>591521</v>
+      </c>
+      <c r="E181">
+        <v>595558</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>24</v>
       </c>
@@ -17446,8 +18726,15 @@
       <c r="C182">
         <v>135843</v>
       </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D182">
+        <f t="shared" si="2"/>
+        <v>431418</v>
+      </c>
+      <c r="E182">
+        <v>567261</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>25</v>
       </c>
@@ -17457,8 +18744,15 @@
       <c r="C183">
         <v>83253</v>
       </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D183">
+        <f t="shared" si="2"/>
+        <v>307523</v>
+      </c>
+      <c r="E183">
+        <v>390776</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>26</v>
       </c>
@@ -17468,8 +18762,15 @@
       <c r="C184">
         <v>20037</v>
       </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D184">
+        <f t="shared" si="2"/>
+        <v>69288</v>
+      </c>
+      <c r="E184">
+        <v>89325</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>27</v>
       </c>
@@ -17479,8 +18780,15 @@
       <c r="C185">
         <v>347117</v>
       </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D185">
+        <f t="shared" si="2"/>
+        <v>1045782</v>
+      </c>
+      <c r="E185">
+        <v>1392899</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>28</v>
       </c>
@@ -17490,8 +18798,15 @@
       <c r="C186">
         <v>5417</v>
       </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D186">
+        <f t="shared" si="2"/>
+        <v>45314</v>
+      </c>
+      <c r="E186">
+        <v>50731</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>29</v>
       </c>
@@ -17501,8 +18816,15 @@
       <c r="C187">
         <v>37455</v>
       </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D187">
+        <f t="shared" si="2"/>
+        <v>134297</v>
+      </c>
+      <c r="E187">
+        <v>171752</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>30</v>
       </c>
@@ -17512,8 +18834,15 @@
       <c r="C188">
         <v>18943</v>
       </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D188">
+        <f t="shared" si="2"/>
+        <v>66206</v>
+      </c>
+      <c r="E188">
+        <v>85149</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>31</v>
       </c>
@@ -17523,8 +18852,15 @@
       <c r="C189">
         <v>257103</v>
       </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D189">
+        <f t="shared" si="2"/>
+        <v>544875</v>
+      </c>
+      <c r="E189">
+        <v>801978</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>32</v>
       </c>
@@ -17534,8 +18870,15 @@
       <c r="C190">
         <v>44111</v>
       </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D190">
+        <f t="shared" si="2"/>
+        <v>262935</v>
+      </c>
+      <c r="E190">
+        <v>307046</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>33</v>
       </c>
@@ -17545,8 +18888,15 @@
       <c r="C191">
         <v>46879</v>
       </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D191">
+        <f t="shared" si="2"/>
+        <v>279179</v>
+      </c>
+      <c r="E191">
+        <v>326058</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>34</v>
       </c>
@@ -17556,8 +18906,15 @@
       <c r="C192">
         <v>652991</v>
       </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D192">
+        <f t="shared" si="2"/>
+        <v>1781246</v>
+      </c>
+      <c r="E192">
+        <v>2434237</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>35</v>
       </c>
@@ -17567,8 +18924,15 @@
       <c r="C193">
         <v>237707</v>
       </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D193">
+        <f t="shared" si="2"/>
+        <v>904604</v>
+      </c>
+      <c r="E193">
+        <v>1142311</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>36</v>
       </c>
@@ -17578,8 +18942,15 @@
       <c r="C194">
         <v>83566</v>
       </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D194">
+        <f t="shared" si="2"/>
+        <v>418210</v>
+      </c>
+      <c r="E194">
+        <v>501776</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>37</v>
       </c>
@@ -17589,8 +18960,15 @@
       <c r="C195">
         <v>182349</v>
       </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D195">
+        <f t="shared" ref="D195:D258" si="3">E195-C195</f>
+        <v>287131</v>
+      </c>
+      <c r="E195">
+        <v>469480</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>38</v>
       </c>
@@ -17600,8 +18978,15 @@
       <c r="C196">
         <v>280272</v>
       </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D196">
+        <f t="shared" si="3"/>
+        <v>1126906</v>
+      </c>
+      <c r="E196">
+        <v>1407178</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>39</v>
       </c>
@@ -17611,8 +18996,15 @@
       <c r="C197">
         <v>34526</v>
       </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D197">
+        <f t="shared" si="3"/>
+        <v>82702</v>
+      </c>
+      <c r="E197">
+        <v>117228</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>40</v>
       </c>
@@ -17622,8 +19014,15 @@
       <c r="C198">
         <v>112772</v>
       </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D198">
+        <f t="shared" si="3"/>
+        <v>484511</v>
+      </c>
+      <c r="E198">
+        <v>597283</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>41</v>
       </c>
@@ -17633,8 +19032,15 @@
       <c r="C199">
         <v>14739</v>
       </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D199">
+        <f t="shared" si="3"/>
+        <v>62605</v>
+      </c>
+      <c r="E199">
+        <v>77344</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>42</v>
       </c>
@@ -17644,8 +19050,15 @@
       <c r="C200">
         <v>180842</v>
       </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D200">
+        <f t="shared" si="3"/>
+        <v>641137</v>
+      </c>
+      <c r="E200">
+        <v>821979</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>43</v>
       </c>
@@ -17655,8 +19068,15 @@
       <c r="C201">
         <v>334075</v>
       </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D201">
+        <f t="shared" si="3"/>
+        <v>2694110</v>
+      </c>
+      <c r="E201">
+        <v>3028185</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>44</v>
       </c>
@@ -17666,8 +19086,15 @@
       <c r="C202">
         <v>34610</v>
       </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D202">
+        <f t="shared" si="3"/>
+        <v>128416</v>
+      </c>
+      <c r="E202">
+        <v>163026</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>45</v>
       </c>
@@ -17677,8 +19104,15 @@
       <c r="C203">
         <v>190582</v>
       </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D203">
+        <f t="shared" si="3"/>
+        <v>601390</v>
+      </c>
+      <c r="E203">
+        <v>791972</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>46</v>
       </c>
@@ -17688,8 +19122,15 @@
       <c r="C204">
         <v>5505</v>
       </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D204">
+        <f t="shared" si="3"/>
+        <v>51457</v>
+      </c>
+      <c r="E204">
+        <v>56962</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>47</v>
       </c>
@@ -17699,8 +19140,15 @@
       <c r="C205">
         <v>66336</v>
       </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D205">
+        <f t="shared" si="3"/>
+        <v>748785</v>
+      </c>
+      <c r="E205">
+        <v>815121</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>48</v>
       </c>
@@ -17710,8 +19158,15 @@
       <c r="C206">
         <v>96751</v>
       </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D206">
+        <f t="shared" si="3"/>
+        <v>438730</v>
+      </c>
+      <c r="E206">
+        <v>535481</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>49</v>
       </c>
@@ -17721,8 +19176,15 @@
       <c r="C207">
         <v>39754</v>
       </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D207">
+        <f t="shared" si="3"/>
+        <v>153271</v>
+      </c>
+      <c r="E207">
+        <v>193025</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>50</v>
       </c>
@@ -17732,8 +19194,15 @@
       <c r="C208">
         <v>6152</v>
       </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D208">
+        <f t="shared" si="3"/>
+        <v>35713</v>
+      </c>
+      <c r="E208">
+        <v>41865</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A209" s="1" t="s">
         <v>63</v>
       </c>
@@ -17744,8 +19213,16 @@
         <f>SUM(C158:C208)</f>
         <v>7213381</v>
       </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D209" s="1">
+        <f t="shared" si="3"/>
+        <v>28357494</v>
+      </c>
+      <c r="E209" s="1">
+        <f>SUM(E158:E208)</f>
+        <v>35570875</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>0</v>
       </c>
@@ -17755,8 +19232,15 @@
       <c r="C210">
         <v>12740</v>
       </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D210">
+        <f t="shared" si="3"/>
+        <v>71819</v>
+      </c>
+      <c r="E210">
+        <v>84559</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>1</v>
       </c>
@@ -17766,8 +19250,15 @@
       <c r="C211">
         <v>198102</v>
       </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D211">
+        <f t="shared" si="3"/>
+        <v>472692</v>
+      </c>
+      <c r="E211">
+        <v>670794</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>2</v>
       </c>
@@ -17777,8 +19268,15 @@
       <c r="C212">
         <v>78477</v>
       </c>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D212">
+        <f t="shared" si="3"/>
+        <v>320374</v>
+      </c>
+      <c r="E212">
+        <v>398851</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>3</v>
       </c>
@@ -17788,8 +19286,15 @@
       <c r="C213">
         <v>109923</v>
       </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D213">
+        <f t="shared" si="3"/>
+        <v>603674</v>
+      </c>
+      <c r="E213">
+        <v>713597</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>4</v>
       </c>
@@ -17799,8 +19304,15 @@
       <c r="C214">
         <v>1249682</v>
       </c>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D214">
+        <f t="shared" si="3"/>
+        <v>3238030</v>
+      </c>
+      <c r="E214">
+        <v>4487712</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>5</v>
       </c>
@@ -17810,8 +19322,15 @@
       <c r="C215">
         <v>137972</v>
       </c>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D215">
+        <f t="shared" si="3"/>
+        <v>388546</v>
+      </c>
+      <c r="E215">
+        <v>526518</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>6</v>
       </c>
@@ -17821,8 +19340,15 @@
       <c r="C216">
         <v>25570</v>
       </c>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D216">
+        <f t="shared" si="3"/>
+        <v>337449</v>
+      </c>
+      <c r="E216">
+        <v>363019</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>7</v>
       </c>
@@ -17832,8 +19358,15 @@
       <c r="C217">
         <v>15713</v>
       </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D217">
+        <f t="shared" si="3"/>
+        <v>77091</v>
+      </c>
+      <c r="E217">
+        <v>92804</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>8</v>
       </c>
@@ -17843,8 +19376,15 @@
       <c r="C218">
         <v>13784</v>
       </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D218">
+        <f t="shared" si="3"/>
+        <v>90849</v>
+      </c>
+      <c r="E218">
+        <v>104633</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>9</v>
       </c>
@@ -17854,8 +19394,15 @@
       <c r="C219">
         <v>171606</v>
       </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D219">
+        <f t="shared" si="3"/>
+        <v>2123101</v>
+      </c>
+      <c r="E219">
+        <v>2294707</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>10</v>
       </c>
@@ -17865,8 +19412,15 @@
       <c r="C220">
         <v>174668</v>
       </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D220">
+        <f t="shared" si="3"/>
+        <v>1114862</v>
+      </c>
+      <c r="E220">
+        <v>1289530</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>11</v>
       </c>
@@ -17876,8 +19430,15 @@
       <c r="C221">
         <v>26010</v>
       </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D221">
+        <f t="shared" si="3"/>
+        <v>128820</v>
+      </c>
+      <c r="E221">
+        <v>154830</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>12</v>
       </c>
@@ -17887,8 +19448,15 @@
       <c r="C222">
         <v>83517</v>
       </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D222">
+        <f t="shared" si="3"/>
+        <v>248461</v>
+      </c>
+      <c r="E222">
+        <v>331978</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>13</v>
       </c>
@@ -17898,8 +19466,15 @@
       <c r="C223">
         <v>19597</v>
       </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D223">
+        <f t="shared" si="3"/>
+        <v>132131</v>
+      </c>
+      <c r="E223">
+        <v>151728</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>14</v>
       </c>
@@ -17909,8 +19484,15 @@
       <c r="C224">
         <v>304742</v>
       </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D224">
+        <f t="shared" si="3"/>
+        <v>1030809</v>
+      </c>
+      <c r="E224">
+        <v>1335551</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>15</v>
       </c>
@@ -17920,8 +19502,15 @@
       <c r="C225">
         <v>117023</v>
       </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D225">
+        <f t="shared" si="3"/>
+        <v>542212</v>
+      </c>
+      <c r="E225">
+        <v>659235</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>16</v>
       </c>
@@ -17931,8 +19520,15 @@
       <c r="C226">
         <v>70832</v>
       </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D226">
+        <f t="shared" si="3"/>
+        <v>200127</v>
+      </c>
+      <c r="E226">
+        <v>270959</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>17</v>
       </c>
@@ -17942,8 +19538,15 @@
       <c r="C227">
         <v>119910</v>
       </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D227">
+        <f t="shared" si="3"/>
+        <v>446239</v>
+      </c>
+      <c r="E227">
+        <v>566149</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>18</v>
       </c>
@@ -17953,8 +19556,15 @@
       <c r="C228">
         <v>131808</v>
       </c>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D228">
+        <f t="shared" si="3"/>
+        <v>515076</v>
+      </c>
+      <c r="E228">
+        <v>646884</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>19</v>
       </c>
@@ -17964,8 +19574,15 @@
       <c r="C229">
         <v>174695</v>
       </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D229">
+        <f t="shared" si="3"/>
+        <v>487563</v>
+      </c>
+      <c r="E229">
+        <v>662258</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>20</v>
       </c>
@@ -17975,8 +19592,15 @@
       <c r="C230">
         <v>196326</v>
       </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D230">
+        <f t="shared" si="3"/>
+        <v>467444</v>
+      </c>
+      <c r="E230">
+        <v>663770</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>21</v>
       </c>
@@ -17986,8 +19610,15 @@
       <c r="C231">
         <v>19858</v>
       </c>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D231">
+        <f t="shared" si="3"/>
+        <v>118190</v>
+      </c>
+      <c r="E231">
+        <v>138048</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>22</v>
       </c>
@@ -17997,8 +19628,15 @@
       <c r="C232">
         <v>165309</v>
       </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D232">
+        <f t="shared" si="3"/>
+        <v>708103</v>
+      </c>
+      <c r="E232">
+        <v>873412</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>23</v>
       </c>
@@ -18008,8 +19646,15 @@
       <c r="C233">
         <v>3968</v>
       </c>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D233">
+        <f t="shared" si="3"/>
+        <v>590911</v>
+      </c>
+      <c r="E233">
+        <v>594879</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>24</v>
       </c>
@@ -18019,8 +19664,15 @@
       <c r="C234">
         <v>132415</v>
       </c>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D234">
+        <f t="shared" si="3"/>
+        <v>433982</v>
+      </c>
+      <c r="E234">
+        <v>566397</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>25</v>
       </c>
@@ -18030,8 +19682,15 @@
       <c r="C235">
         <v>83125</v>
       </c>
-    </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D235">
+        <f t="shared" si="3"/>
+        <v>306455</v>
+      </c>
+      <c r="E235">
+        <v>389580</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>26</v>
       </c>
@@ -18041,8 +19700,15 @@
       <c r="C236">
         <v>19544</v>
       </c>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D236">
+        <f t="shared" si="3"/>
+        <v>67544</v>
+      </c>
+      <c r="E236">
+        <v>87088</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>27</v>
       </c>
@@ -18052,8 +19718,15 @@
       <c r="C237">
         <v>349014</v>
       </c>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D237">
+        <f t="shared" si="3"/>
+        <v>1031283</v>
+      </c>
+      <c r="E237">
+        <v>1380297</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>28</v>
       </c>
@@ -18063,8 +19736,15 @@
       <c r="C238">
         <v>5410</v>
       </c>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D238">
+        <f t="shared" si="3"/>
+        <v>45244</v>
+      </c>
+      <c r="E238">
+        <v>50654</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>29</v>
       </c>
@@ -18074,8 +19754,15 @@
       <c r="C239">
         <v>35874</v>
       </c>
-    </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D239">
+        <f t="shared" si="3"/>
+        <v>133785</v>
+      </c>
+      <c r="E239">
+        <v>169659</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>30</v>
       </c>
@@ -18085,8 +19772,15 @@
       <c r="C240">
         <v>18915</v>
       </c>
-    </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D240">
+        <f t="shared" si="3"/>
+        <v>66076</v>
+      </c>
+      <c r="E240">
+        <v>84991</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>31</v>
       </c>
@@ -18096,8 +19790,15 @@
       <c r="C241">
         <v>261154</v>
       </c>
-    </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D241">
+        <f t="shared" si="3"/>
+        <v>547526</v>
+      </c>
+      <c r="E241">
+        <v>808680</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>32</v>
       </c>
@@ -18107,8 +19808,15 @@
       <c r="C242">
         <v>42494</v>
       </c>
-    </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D242">
+        <f t="shared" si="3"/>
+        <v>264188</v>
+      </c>
+      <c r="E242">
+        <v>306682</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>33</v>
       </c>
@@ -18118,8 +19826,15 @@
       <c r="C243">
         <v>46080</v>
       </c>
-    </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D243">
+        <f t="shared" si="3"/>
+        <v>266697</v>
+      </c>
+      <c r="E243">
+        <v>312777</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>34</v>
       </c>
@@ -18129,8 +19844,15 @@
       <c r="C244">
         <v>650335</v>
       </c>
-    </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D244">
+        <f t="shared" si="3"/>
+        <v>1779024</v>
+      </c>
+      <c r="E244">
+        <v>2429359</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>35</v>
       </c>
@@ -18140,8 +19862,15 @@
       <c r="C245">
         <v>232871</v>
       </c>
-    </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D245">
+        <f t="shared" si="3"/>
+        <v>896895</v>
+      </c>
+      <c r="E245">
+        <v>1129766</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>36</v>
       </c>
@@ -18151,8 +19880,15 @@
       <c r="C246">
         <v>81057</v>
       </c>
-    </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D246">
+        <f t="shared" si="3"/>
+        <v>421620</v>
+      </c>
+      <c r="E246">
+        <v>502677</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>37</v>
       </c>
@@ -18162,8 +19898,15 @@
       <c r="C247">
         <v>180746</v>
       </c>
-    </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D247">
+        <f t="shared" si="3"/>
+        <v>287248</v>
+      </c>
+      <c r="E247">
+        <v>467994</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>38</v>
       </c>
@@ -18173,8 +19916,15 @@
       <c r="C248">
         <v>277094</v>
       </c>
-    </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D248">
+        <f t="shared" si="3"/>
+        <v>1123335</v>
+      </c>
+      <c r="E248">
+        <v>1400429</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>39</v>
       </c>
@@ -18184,8 +19934,15 @@
       <c r="C249">
         <v>33766</v>
       </c>
-    </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D249">
+        <f t="shared" si="3"/>
+        <v>82732</v>
+      </c>
+      <c r="E249">
+        <v>116498</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>40</v>
       </c>
@@ -18195,8 +19952,15 @@
       <c r="C250">
         <v>112428</v>
       </c>
-    </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D250">
+        <f t="shared" si="3"/>
+        <v>484874</v>
+      </c>
+      <c r="E250">
+        <v>597302</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>41</v>
       </c>
@@ -18206,8 +19970,15 @@
       <c r="C251">
         <v>14453</v>
       </c>
-    </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D251">
+        <f t="shared" si="3"/>
+        <v>61945</v>
+      </c>
+      <c r="E251">
+        <v>76398</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>42</v>
       </c>
@@ -18217,8 +19988,15 @@
       <c r="C252">
         <v>181381</v>
       </c>
-    </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D252">
+        <f t="shared" si="3"/>
+        <v>640928</v>
+      </c>
+      <c r="E252">
+        <v>822309</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>43</v>
       </c>
@@ -18228,8 +20006,15 @@
       <c r="C253">
         <v>333003</v>
       </c>
-    </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D253">
+        <f t="shared" si="3"/>
+        <v>2683769</v>
+      </c>
+      <c r="E253">
+        <v>3016772</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>44</v>
       </c>
@@ -18239,8 +20024,15 @@
       <c r="C254">
         <v>34242</v>
       </c>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D254">
+        <f t="shared" si="3"/>
+        <v>127477</v>
+      </c>
+      <c r="E254">
+        <v>161719</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>45</v>
       </c>
@@ -18250,8 +20042,15 @@
       <c r="C255">
         <v>189054</v>
       </c>
-    </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D255">
+        <f t="shared" si="3"/>
+        <v>600395</v>
+      </c>
+      <c r="E255">
+        <v>789449</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>46</v>
       </c>
@@ -18261,8 +20060,15 @@
       <c r="C256">
         <v>5527</v>
       </c>
-    </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D256">
+        <f t="shared" si="3"/>
+        <v>51196</v>
+      </c>
+      <c r="E256">
+        <v>56723</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>47</v>
       </c>
@@ -18272,8 +20078,15 @@
       <c r="C257">
         <v>61666</v>
       </c>
-    </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D257">
+        <f t="shared" si="3"/>
+        <v>752954</v>
+      </c>
+      <c r="E257">
+        <v>814620</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>48</v>
       </c>
@@ -18283,8 +20096,15 @@
       <c r="C258">
         <v>97222</v>
       </c>
-    </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D258">
+        <f t="shared" si="3"/>
+        <v>435349</v>
+      </c>
+      <c r="E258">
+        <v>532571</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>49</v>
       </c>
@@ -18294,8 +20114,15 @@
       <c r="C259">
         <v>39040</v>
       </c>
-    </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D259">
+        <f t="shared" ref="D259:D261" si="4">E259-C259</f>
+        <v>153779</v>
+      </c>
+      <c r="E259">
+        <v>192819</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>50</v>
       </c>
@@ -18305,8 +20132,15 @@
       <c r="C260">
         <v>6065</v>
       </c>
-    </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D260">
+        <f t="shared" si="4"/>
+        <v>34770</v>
+      </c>
+      <c r="E260">
+        <v>40835</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A261" s="1" t="s">
         <v>63</v>
       </c>
@@ -18316,6 +20150,14 @@
       <c r="C261" s="1">
         <f>SUM(C210:C260)</f>
         <v>7145807</v>
+      </c>
+      <c r="D261" s="1">
+        <f>E261-C261</f>
+        <v>28235643</v>
+      </c>
+      <c r="E261" s="1">
+        <f>SUM(E210:E260)</f>
+        <v>35381450</v>
       </c>
     </row>
   </sheetData>
@@ -18325,15 +20167,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873D0142-E9C6-4992-9A6E-21A65D208859}">
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>51</v>
       </c>
@@ -18343,8 +20187,14 @@
       <c r="C1" s="1" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -18354,8 +20204,15 @@
       <c r="C2">
         <v>12150</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D2">
+        <f>E2-C2</f>
+        <v>93516</v>
+      </c>
+      <c r="E2">
+        <v>105666</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -18365,8 +20222,15 @@
       <c r="C3">
         <v>205536</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D3">
+        <f>E3-C3</f>
+        <v>596195</v>
+      </c>
+      <c r="E3">
+        <v>801731</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -18376,8 +20240,15 @@
       <c r="C4">
         <v>75026</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D4">
+        <f>E4-C4</f>
+        <v>404879</v>
+      </c>
+      <c r="E4">
+        <v>479905</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -18387,8 +20258,14 @@
       <c r="C5">
         <v>147213</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D5" t="s">
+        <v>156</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -18398,8 +20275,15 @@
       <c r="C6">
         <v>1297814</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D6">
+        <f>E6-C6</f>
+        <v>3997740</v>
+      </c>
+      <c r="E6">
+        <v>5295554</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -18409,8 +20293,15 @@
       <c r="C7">
         <v>119896</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D7">
+        <f>E7-C7</f>
+        <v>533164</v>
+      </c>
+      <c r="E7">
+        <v>653060</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -18420,8 +20311,15 @@
       <c r="C8">
         <v>13667</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D8">
+        <f>E8-C8</f>
+        <v>357501</v>
+      </c>
+      <c r="E8">
+        <v>371168</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -18431,8 +20329,15 @@
       <c r="C9">
         <v>16242</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D9">
+        <f>E9-C9</f>
+        <v>84946</v>
+      </c>
+      <c r="E9">
+        <v>101188</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -18442,8 +20347,15 @@
       <c r="C10">
         <v>6541</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D10">
+        <f>E10-C10</f>
+        <v>118352</v>
+      </c>
+      <c r="E10">
+        <v>124893</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -18453,8 +20365,15 @@
       <c r="C11">
         <v>87798</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D11">
+        <f>E11-C11</f>
+        <v>3006508</v>
+      </c>
+      <c r="E11">
+        <v>3094306</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -18464,8 +20383,15 @@
       <c r="C12">
         <v>325706</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D12">
+        <f>E12-C12</f>
+        <v>1411272</v>
+      </c>
+      <c r="E12">
+        <v>1736978</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -18475,8 +20401,15 @@
       <c r="C13">
         <v>24181</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D13">
+        <f>E13-C13</f>
+        <v>142118</v>
+      </c>
+      <c r="E13">
+        <v>166299</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -18486,8 +20419,15 @@
       <c r="C14">
         <v>69846</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D14">
+        <f>E14-C14</f>
+        <v>318341</v>
+      </c>
+      <c r="E14">
+        <v>388187</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -18497,8 +20437,15 @@
       <c r="C15">
         <v>39369</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D15">
+        <f>E15-C15</f>
+        <v>172679</v>
+      </c>
+      <c r="E15">
+        <v>212048</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -18508,8 +20455,15 @@
       <c r="C16">
         <v>346416</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D16">
+        <f>E16-C16</f>
+        <v>1227847</v>
+      </c>
+      <c r="E16">
+        <v>1574263</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -18519,8 +20473,15 @@
       <c r="C17">
         <v>136704</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D17">
+        <f>E17-C17</f>
+        <v>750949</v>
+      </c>
+      <c r="E17">
+        <v>887653</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -18530,8 +20491,15 @@
       <c r="C18">
         <v>68364</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D18">
+        <f>E18-C18</f>
+        <v>269538</v>
+      </c>
+      <c r="E18">
+        <v>337902</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -18541,8 +20509,15 @@
       <c r="C19">
         <v>143601</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D19">
+        <f>E19-C19</f>
+        <v>505675</v>
+      </c>
+      <c r="E19">
+        <v>649276</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -18552,8 +20527,15 @@
       <c r="C20">
         <v>189203</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D20">
+        <f>E20-C20</f>
+        <v>616118</v>
+      </c>
+      <c r="E20">
+        <v>805321</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -18563,8 +20545,15 @@
       <c r="C21">
         <v>210420</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D21">
+        <f>E21-C21</f>
+        <v>554415</v>
+      </c>
+      <c r="E21">
+        <v>764835</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -18574,8 +20563,15 @@
       <c r="C22">
         <v>166163</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D22">
+        <f>E22-C22</f>
+        <v>567504</v>
+      </c>
+      <c r="E22">
+        <v>733667</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -18585,8 +20581,15 @@
       <c r="C23">
         <v>15641</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D23">
+        <f>E23-C23</f>
+        <v>122548</v>
+      </c>
+      <c r="E23">
+        <v>138189</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -18596,8 +20599,15 @@
       <c r="C24">
         <v>143833</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D24">
+        <f>E24-C24</f>
+        <v>989818</v>
+      </c>
+      <c r="E24">
+        <v>1133651</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -18607,8 +20617,15 @@
       <c r="C25">
         <v>3313</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D25">
+        <f>E25-C25</f>
+        <v>640361</v>
+      </c>
+      <c r="E25">
+        <v>643674</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -18618,8 +20635,15 @@
       <c r="C26">
         <v>39895</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D26">
+        <f>E26-C26</f>
+        <v>715873</v>
+      </c>
+      <c r="E26">
+        <v>755768</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -18629,8 +20653,15 @@
       <c r="C27">
         <v>77568</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D27">
+        <f>E27-C27</f>
+        <v>402777</v>
+      </c>
+      <c r="E27">
+        <v>480345</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -18640,8 +20671,15 @@
       <c r="C28">
         <v>28814</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D28">
+        <f>E28-C28</f>
+        <v>104038</v>
+      </c>
+      <c r="E28">
+        <v>132852</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -18651,8 +20689,15 @@
       <c r="C29">
         <v>300301</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D29">
+        <f>E29-C29</f>
+        <v>1106530</v>
+      </c>
+      <c r="E29">
+        <v>1406831</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -18662,8 +20707,15 @@
       <c r="C30">
         <v>3881</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D30">
+        <f>E30-C30</f>
+        <v>55827</v>
+      </c>
+      <c r="E30">
+        <v>59708</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -18673,8 +20725,15 @@
       <c r="C31">
         <v>42529</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D31">
+        <f>E31-C31</f>
+        <v>161824</v>
+      </c>
+      <c r="E31">
+        <v>204353</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -18684,8 +20743,15 @@
       <c r="C32">
         <v>23704</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D32">
+        <f>E32-C32</f>
+        <v>84159</v>
+      </c>
+      <c r="E32">
+        <v>107863</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>31</v>
       </c>
@@ -18695,8 +20761,15 @@
       <c r="C33">
         <v>268685</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D33">
+        <f>E33-C33</f>
+        <v>693281</v>
+      </c>
+      <c r="E33">
+        <v>961966</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -18706,8 +20779,15 @@
       <c r="C34">
         <v>54184</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D34">
+        <f>E34-C34</f>
+        <v>331330</v>
+      </c>
+      <c r="E34">
+        <v>385514</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -18717,8 +20797,15 @@
       <c r="C35">
         <v>55698</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D35">
+        <f>E35-C35</f>
+        <v>309696</v>
+      </c>
+      <c r="E35">
+        <v>365394</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -18728,8 +20815,15 @@
       <c r="C36">
         <v>529246</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D36">
+        <f>E36-C36</f>
+        <v>2096997</v>
+      </c>
+      <c r="E36">
+        <v>2626243</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -18739,8 +20833,15 @@
       <c r="C37">
         <v>254452</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D37">
+        <f>E37-C37</f>
+        <v>1109449</v>
+      </c>
+      <c r="E37">
+        <v>1363901</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>36</v>
       </c>
@@ -18750,8 +20851,15 @@
       <c r="C38">
         <v>143251</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D38">
+        <f>E38-C38</f>
+        <v>507919</v>
+      </c>
+      <c r="E38">
+        <v>651170</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -18761,8 +20869,15 @@
       <c r="C39">
         <v>188991</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D39">
+        <f>E39-C39</f>
+        <v>305649</v>
+      </c>
+      <c r="E39">
+        <v>494640</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -18772,8 +20887,15 @@
       <c r="C40">
         <v>250984</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D40">
+        <f>E40-C40</f>
+        <v>1333346</v>
+      </c>
+      <c r="E40">
+        <v>1584330</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -18783,8 +20905,15 @@
       <c r="C41">
         <v>37124</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D41">
+        <f>E41-C41</f>
+        <v>92887</v>
+      </c>
+      <c r="E41">
+        <v>130011</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -18794,8 +20923,15 @@
       <c r="C42">
         <v>111786</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D42">
+        <f>E42-C42</f>
+        <v>648153</v>
+      </c>
+      <c r="E42">
+        <v>759939</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>41</v>
       </c>
@@ -18805,8 +20941,15 @@
       <c r="C43">
         <v>19452</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D43">
+        <f>E43-C43</f>
+        <v>82683</v>
+      </c>
+      <c r="E43">
+        <v>102135</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>42</v>
       </c>
@@ -18816,8 +20959,15 @@
       <c r="C44">
         <v>148032</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D44">
+        <f>E44-C44</f>
+        <v>801706</v>
+      </c>
+      <c r="E44">
+        <v>949738</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -18827,8 +20977,15 @@
       <c r="C45">
         <v>281452</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D45">
+        <f>E45-C45</f>
+        <v>4090702</v>
+      </c>
+      <c r="E45">
+        <v>4372154</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -18838,8 +20995,15 @@
       <c r="C46">
         <v>38339</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D46">
+        <f>E46-C46</f>
+        <v>201228</v>
+      </c>
+      <c r="E46">
+        <v>239567</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>45</v>
       </c>
@@ -18849,8 +21013,15 @@
       <c r="C47">
         <v>192748</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D47">
+        <f>E47-C47</f>
+        <v>744703</v>
+      </c>
+      <c r="E47">
+        <v>937451</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>46</v>
       </c>
@@ -18860,8 +21031,15 @@
       <c r="C48">
         <v>4584</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D48">
+        <f>E48-C48</f>
+        <v>60863</v>
+      </c>
+      <c r="E48">
+        <v>65447</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>47</v>
       </c>
@@ -18871,8 +21049,15 @@
       <c r="C49">
         <v>80027</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D49">
+        <f>E49-C49</f>
+        <v>830541</v>
+      </c>
+      <c r="E49">
+        <v>910568</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>48</v>
       </c>
@@ -18882,8 +21067,15 @@
       <c r="C50">
         <v>79903</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D50">
+        <f>E50-C50</f>
+        <v>568864</v>
+      </c>
+      <c r="E50">
+        <v>648767</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>49</v>
       </c>
@@ -18893,8 +21085,15 @@
       <c r="C51">
         <v>37872</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D51">
+        <f>E51-C51</f>
+        <v>200202</v>
+      </c>
+      <c r="E51">
+        <v>238074</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>50</v>
       </c>
@@ -18904,8 +21103,15 @@
       <c r="C52">
         <v>5303</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D52">
+        <f>E52-C52</f>
+        <v>48085</v>
+      </c>
+      <c r="E52">
+        <v>53388</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>63</v>
       </c>
@@ -18915,6 +21121,14 @@
       <c r="C53" s="1">
         <f>SUM(C2:C52)</f>
         <v>7163448</v>
+      </c>
+      <c r="D53" s="1">
+        <f>SUM(D2:D52)</f>
+        <v>35171296</v>
+      </c>
+      <c r="E53" s="1">
+        <f>SUM(E2:E52)</f>
+        <v>42187531</v>
       </c>
     </row>
   </sheetData>

--- a/data/Enrollment_Tracker.xlsx
+++ b/data/Enrollment_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ahausa-my.sharepoint.com/personal/inicchitta_aha_org/Documents/Documents/Projects/Enrollment Tracking/project/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{F42CCC4A-64CB-4D65-8DF8-D273176EBD5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0E06663-B712-4E6F-9C1A-59742C3F41D1}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{F42CCC4A-64CB-4D65-8DF8-D273176EBD5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FA63906-57DC-42CA-9B5A-68D84F0C94A7}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{ABF58F20-35C5-4B4F-8D44-F14F003A923B}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{ABF58F20-35C5-4B4F-8D44-F14F003A923B}"/>
   </bookViews>
   <sheets>
     <sheet name="Mcaid" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2607" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2919" uniqueCount="157">
   <si>
     <t>Alaska</t>
   </si>
@@ -28383,7 +28383,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9AC6405-B94F-4AB6-9B77-14A04AE8F552}">
-  <dimension ref="A1:R313"/>
+  <dimension ref="A1:R469"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
@@ -35319,6 +35319,1731 @@
         <v>82</v>
       </c>
     </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>0</v>
+      </c>
+      <c r="B314" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C314" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>1</v>
+      </c>
+      <c r="B315" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C315" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>2</v>
+      </c>
+      <c r="B316" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C316" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>3</v>
+      </c>
+      <c r="B317" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C317" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>65</v>
+      </c>
+      <c r="B318" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C318" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>66</v>
+      </c>
+      <c r="B319" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C319" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>67</v>
+      </c>
+      <c r="B320" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C320" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>68</v>
+      </c>
+      <c r="B321" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C321" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>8</v>
+      </c>
+      <c r="B322" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C322" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>9</v>
+      </c>
+      <c r="B323" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C323" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>10</v>
+      </c>
+      <c r="B324" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C324" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>11</v>
+      </c>
+      <c r="B325" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C325" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>12</v>
+      </c>
+      <c r="B326" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C326" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>69</v>
+      </c>
+      <c r="B327" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C327" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>14</v>
+      </c>
+      <c r="B328" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C328" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>15</v>
+      </c>
+      <c r="B329" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C329" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>16</v>
+      </c>
+      <c r="B330" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C330" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>17</v>
+      </c>
+      <c r="B331" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C331" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>18</v>
+      </c>
+      <c r="B332" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C332" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>70</v>
+      </c>
+      <c r="B333" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C333" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>20</v>
+      </c>
+      <c r="B334" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C334" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>21</v>
+      </c>
+      <c r="B335" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C335" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>22</v>
+      </c>
+      <c r="B336" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C336" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>23</v>
+      </c>
+      <c r="B337" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C337" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>24</v>
+      </c>
+      <c r="B338" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C338" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>25</v>
+      </c>
+      <c r="B339" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C339" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>26</v>
+      </c>
+      <c r="B340" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C340" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>27</v>
+      </c>
+      <c r="B341" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C341" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>28</v>
+      </c>
+      <c r="B342" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C342" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>29</v>
+      </c>
+      <c r="B343" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C343" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>30</v>
+      </c>
+      <c r="B344" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C344" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>31</v>
+      </c>
+      <c r="B345" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C345" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>32</v>
+      </c>
+      <c r="B346" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C346" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>33</v>
+      </c>
+      <c r="B347" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C347" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>34</v>
+      </c>
+      <c r="B348" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C348" t="s">
+        <v>74</v>
+      </c>
+      <c r="D348">
+        <v>251283</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>35</v>
+      </c>
+      <c r="B349" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C349" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>36</v>
+      </c>
+      <c r="B350" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C350" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>37</v>
+      </c>
+      <c r="B351" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C351" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>38</v>
+      </c>
+      <c r="B352" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C352" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>71</v>
+      </c>
+      <c r="B353" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C353" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>40</v>
+      </c>
+      <c r="B354" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C354" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>41</v>
+      </c>
+      <c r="B355" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C355" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>42</v>
+      </c>
+      <c r="B356" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C356" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>43</v>
+      </c>
+      <c r="B357" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C357" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>44</v>
+      </c>
+      <c r="B358" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C358" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>45</v>
+      </c>
+      <c r="B359" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C359" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>46</v>
+      </c>
+      <c r="B360" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C360" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>72</v>
+      </c>
+      <c r="B361" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C361" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>48</v>
+      </c>
+      <c r="B362" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C362" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>49</v>
+      </c>
+      <c r="B363" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C363" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>50</v>
+      </c>
+      <c r="B364" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C364" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>63</v>
+      </c>
+      <c r="B365" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C365" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>0</v>
+      </c>
+      <c r="B366" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C366" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>1</v>
+      </c>
+      <c r="B367" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C367" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>2</v>
+      </c>
+      <c r="B368" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C368" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>3</v>
+      </c>
+      <c r="B369" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C369" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>65</v>
+      </c>
+      <c r="B370" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C370" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>66</v>
+      </c>
+      <c r="B371" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C371" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>67</v>
+      </c>
+      <c r="B372" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C372" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>68</v>
+      </c>
+      <c r="B373" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C373" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>8</v>
+      </c>
+      <c r="B374" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C374" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>9</v>
+      </c>
+      <c r="B375" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C375" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>10</v>
+      </c>
+      <c r="B376" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C376" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>11</v>
+      </c>
+      <c r="B377" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C377" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>12</v>
+      </c>
+      <c r="B378" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C378" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>69</v>
+      </c>
+      <c r="B379" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C379" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>14</v>
+      </c>
+      <c r="B380" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C380" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>15</v>
+      </c>
+      <c r="B381" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C381" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>16</v>
+      </c>
+      <c r="B382" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C382" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>17</v>
+      </c>
+      <c r="B383" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C383" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>18</v>
+      </c>
+      <c r="B384" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C384" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>70</v>
+      </c>
+      <c r="B385" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C385" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>20</v>
+      </c>
+      <c r="B386" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C386" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>21</v>
+      </c>
+      <c r="B387" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C387" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>22</v>
+      </c>
+      <c r="B388" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C388" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>23</v>
+      </c>
+      <c r="B389" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C389" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>24</v>
+      </c>
+      <c r="B390" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C390" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>25</v>
+      </c>
+      <c r="B391" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C391" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>26</v>
+      </c>
+      <c r="B392" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C392" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>27</v>
+      </c>
+      <c r="B393" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C393" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>28</v>
+      </c>
+      <c r="B394" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C394" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>29</v>
+      </c>
+      <c r="B395" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C395" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>30</v>
+      </c>
+      <c r="B396" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C396" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>31</v>
+      </c>
+      <c r="B397" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C397" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>32</v>
+      </c>
+      <c r="B398" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C398" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>33</v>
+      </c>
+      <c r="B399" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C399" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
+        <v>34</v>
+      </c>
+      <c r="B400" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C400" t="s">
+        <v>74</v>
+      </c>
+      <c r="D400">
+        <v>263728</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A401" t="s">
+        <v>35</v>
+      </c>
+      <c r="B401" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C401" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A402" t="s">
+        <v>36</v>
+      </c>
+      <c r="B402" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C402" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A403" t="s">
+        <v>37</v>
+      </c>
+      <c r="B403" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C403" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A404" t="s">
+        <v>38</v>
+      </c>
+      <c r="B404" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C404" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A405" t="s">
+        <v>71</v>
+      </c>
+      <c r="B405" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C405" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A406" t="s">
+        <v>40</v>
+      </c>
+      <c r="B406" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C406" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A407" t="s">
+        <v>41</v>
+      </c>
+      <c r="B407" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C407" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A408" t="s">
+        <v>42</v>
+      </c>
+      <c r="B408" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C408" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A409" t="s">
+        <v>43</v>
+      </c>
+      <c r="B409" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C409" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A410" t="s">
+        <v>44</v>
+      </c>
+      <c r="B410" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C410" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A411" t="s">
+        <v>45</v>
+      </c>
+      <c r="B411" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C411" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A412" t="s">
+        <v>46</v>
+      </c>
+      <c r="B412" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C412" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A413" t="s">
+        <v>72</v>
+      </c>
+      <c r="B413" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C413" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A414" t="s">
+        <v>48</v>
+      </c>
+      <c r="B414" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C414" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A415" t="s">
+        <v>49</v>
+      </c>
+      <c r="B415" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C415" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A416" t="s">
+        <v>50</v>
+      </c>
+      <c r="B416" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C416" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A417" t="s">
+        <v>63</v>
+      </c>
+      <c r="B417" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C417" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A418" t="s">
+        <v>0</v>
+      </c>
+      <c r="B418" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C418" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A419" t="s">
+        <v>1</v>
+      </c>
+      <c r="B419" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C419" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A420" t="s">
+        <v>2</v>
+      </c>
+      <c r="B420" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C420" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A421" t="s">
+        <v>3</v>
+      </c>
+      <c r="B421" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C421" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A422" t="s">
+        <v>65</v>
+      </c>
+      <c r="B422" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C422" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A423" t="s">
+        <v>66</v>
+      </c>
+      <c r="B423" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C423" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A424" t="s">
+        <v>67</v>
+      </c>
+      <c r="B424" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C424" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A425" t="s">
+        <v>68</v>
+      </c>
+      <c r="B425" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C425" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A426" t="s">
+        <v>8</v>
+      </c>
+      <c r="B426" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C426" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A427" t="s">
+        <v>9</v>
+      </c>
+      <c r="B427" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C427" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A428" t="s">
+        <v>10</v>
+      </c>
+      <c r="B428" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C428" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A429" t="s">
+        <v>11</v>
+      </c>
+      <c r="B429" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C429" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A430" t="s">
+        <v>12</v>
+      </c>
+      <c r="B430" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C430" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A431" t="s">
+        <v>69</v>
+      </c>
+      <c r="B431" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C431" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A432" t="s">
+        <v>14</v>
+      </c>
+      <c r="B432" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C432" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A433" t="s">
+        <v>15</v>
+      </c>
+      <c r="B433" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C433" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A434" t="s">
+        <v>16</v>
+      </c>
+      <c r="B434" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C434" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A435" t="s">
+        <v>17</v>
+      </c>
+      <c r="B435" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C435" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A436" t="s">
+        <v>18</v>
+      </c>
+      <c r="B436" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C436" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A437" t="s">
+        <v>70</v>
+      </c>
+      <c r="B437" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C437" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A438" t="s">
+        <v>20</v>
+      </c>
+      <c r="B438" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C438" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A439" t="s">
+        <v>21</v>
+      </c>
+      <c r="B439" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C439" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="440" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A440" t="s">
+        <v>22</v>
+      </c>
+      <c r="B440" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C440" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="441" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A441" t="s">
+        <v>23</v>
+      </c>
+      <c r="B441" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C441" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="442" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A442" t="s">
+        <v>24</v>
+      </c>
+      <c r="B442" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C442" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A443" t="s">
+        <v>25</v>
+      </c>
+      <c r="B443" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C443" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A444" t="s">
+        <v>26</v>
+      </c>
+      <c r="B444" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C444" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A445" t="s">
+        <v>27</v>
+      </c>
+      <c r="B445" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C445" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A446" t="s">
+        <v>28</v>
+      </c>
+      <c r="B446" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C446" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A447" t="s">
+        <v>29</v>
+      </c>
+      <c r="B447" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C447" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A448" t="s">
+        <v>30</v>
+      </c>
+      <c r="B448" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C448" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A449" t="s">
+        <v>31</v>
+      </c>
+      <c r="B449" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C449" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A450" t="s">
+        <v>32</v>
+      </c>
+      <c r="B450" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C450" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A451" t="s">
+        <v>33</v>
+      </c>
+      <c r="B451" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C451" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A452" t="s">
+        <v>34</v>
+      </c>
+      <c r="B452" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C452" t="s">
+        <v>74</v>
+      </c>
+      <c r="D452">
+        <v>270050</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A453" t="s">
+        <v>35</v>
+      </c>
+      <c r="B453" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C453" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A454" t="s">
+        <v>36</v>
+      </c>
+      <c r="B454" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C454" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="455" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A455" t="s">
+        <v>37</v>
+      </c>
+      <c r="B455" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C455" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="456" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A456" t="s">
+        <v>38</v>
+      </c>
+      <c r="B456" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C456" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="457" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A457" t="s">
+        <v>71</v>
+      </c>
+      <c r="B457" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C457" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="458" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A458" t="s">
+        <v>40</v>
+      </c>
+      <c r="B458" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C458" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="459" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A459" t="s">
+        <v>41</v>
+      </c>
+      <c r="B459" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C459" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="460" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A460" t="s">
+        <v>42</v>
+      </c>
+      <c r="B460" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C460" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="461" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A461" t="s">
+        <v>43</v>
+      </c>
+      <c r="B461" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C461" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="462" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A462" t="s">
+        <v>44</v>
+      </c>
+      <c r="B462" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C462" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="463" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A463" t="s">
+        <v>45</v>
+      </c>
+      <c r="B463" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C463" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="464" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A464" t="s">
+        <v>46</v>
+      </c>
+      <c r="B464" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C464" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="465" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A465" t="s">
+        <v>72</v>
+      </c>
+      <c r="B465" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C465" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A466" t="s">
+        <v>48</v>
+      </c>
+      <c r="B466" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C466" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A467" t="s">
+        <v>49</v>
+      </c>
+      <c r="B467" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C467" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A468" t="s">
+        <v>50</v>
+      </c>
+      <c r="B468" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C468" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="469" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A469" t="s">
+        <v>63</v>
+      </c>
+      <c r="B469" s="3">
+        <v>46235</v>
+      </c>
+      <c r="C469" t="s">
+        <v>82</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:A313" xr:uid="{F500077B-CC04-42DE-B4CB-18359DAB49B8}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
